--- a/sources/02032026/Liga2026-ParejasIniciales-Provisional.xlsx
+++ b/sources/02032026/Liga2026-ParejasIniciales-Provisional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hermosil\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2667F12A-661B-4F86-9513-70EEB75277F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF1C412-4DC9-43D2-A1A7-C278197133B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="327">
   <si>
     <t>Division</t>
   </si>
@@ -204,9 +204,6 @@
     <t>Manuel Cruz</t>
   </si>
   <si>
-    <t>Luis Medina</t>
-  </si>
-  <si>
     <t>Jesús Serra</t>
   </si>
   <si>
@@ -384,9 +381,6 @@
     <t>Javi Barrios</t>
   </si>
   <si>
-    <t>Ray Jiménez</t>
-  </si>
-  <si>
     <t>Sergio Serra</t>
   </si>
   <si>
@@ -589,13 +583,445 @@
   </si>
   <si>
     <t>Rafa Robles</t>
+  </si>
+  <si>
+    <t>Grego - Luis Ángel</t>
+  </si>
+  <si>
+    <t>78,25</t>
+  </si>
+  <si>
+    <t>156,5</t>
+  </si>
+  <si>
+    <t>Happy - Pedro Correas</t>
+  </si>
+  <si>
+    <t>89,75</t>
+  </si>
+  <si>
+    <t>83,5</t>
+  </si>
+  <si>
+    <t>173,25</t>
+  </si>
+  <si>
+    <t>Junior - Alfonsito</t>
+  </si>
+  <si>
+    <t>Tote - Antonio Gálvez</t>
+  </si>
+  <si>
+    <t>102,5</t>
+  </si>
+  <si>
+    <t>215,5</t>
+  </si>
+  <si>
+    <t>Santi Molina - Gusi</t>
+  </si>
+  <si>
+    <t>85,25</t>
+  </si>
+  <si>
+    <t>72,25</t>
+  </si>
+  <si>
+    <t>157,5</t>
+  </si>
+  <si>
+    <t>Manolo Gómez - Joaquín Gea</t>
+  </si>
+  <si>
+    <t>91,75</t>
+  </si>
+  <si>
+    <t>183,5</t>
+  </si>
+  <si>
+    <t>Jose Ramón - Ramón Piedra</t>
+  </si>
+  <si>
+    <t>168,25</t>
+  </si>
+  <si>
+    <t>Fabián Morata - Raúl Olivetti</t>
+  </si>
+  <si>
+    <t>166,75</t>
+  </si>
+  <si>
+    <t>Albertillo - Marcos Moreno</t>
+  </si>
+  <si>
+    <t>127,27</t>
+  </si>
+  <si>
+    <t>Curro - Julio Carabias</t>
+  </si>
+  <si>
+    <t>127,75</t>
+  </si>
+  <si>
+    <t>Manuel Choto - Julián</t>
+  </si>
+  <si>
+    <t>Álvaro Molina - Jesús Rodrigo</t>
+  </si>
+  <si>
+    <t>87,75</t>
+  </si>
+  <si>
+    <t>Javi Castillo - Sergio Campoy</t>
+  </si>
+  <si>
+    <t>93,25</t>
+  </si>
+  <si>
+    <t>162,25</t>
+  </si>
+  <si>
+    <t>Loren Portillo - Juanmi Sanabria</t>
+  </si>
+  <si>
+    <t>92,25</t>
+  </si>
+  <si>
+    <t>David Bellido - Manuel Bellido</t>
+  </si>
+  <si>
+    <t>Pablo Cano - Víctor Ocaña</t>
+  </si>
+  <si>
+    <t>93,75</t>
+  </si>
+  <si>
+    <t>Fran Collado - Mariano</t>
+  </si>
+  <si>
+    <t>70,5</t>
+  </si>
+  <si>
+    <t>Juanjo - Juan Carlos Illescas</t>
+  </si>
+  <si>
+    <t>33,25</t>
+  </si>
+  <si>
+    <t>95,25</t>
+  </si>
+  <si>
+    <t>Vivi - Juan Sánchez Sr.</t>
+  </si>
+  <si>
+    <t>30,25</t>
+  </si>
+  <si>
+    <t>98,25</t>
+  </si>
+  <si>
+    <t>Raúl Garcia - Alvarito</t>
+  </si>
+  <si>
+    <t>Adrian Camacho - David Hermosilla</t>
+  </si>
+  <si>
+    <t>Luis Mena - Carlos Domínguez</t>
+  </si>
+  <si>
+    <t>Juanji - Pedro Utrera</t>
+  </si>
+  <si>
+    <t>69,75</t>
+  </si>
+  <si>
+    <t>Loren Perea - Manuel Ortega</t>
+  </si>
+  <si>
+    <t>59,5</t>
+  </si>
+  <si>
+    <t>114,5</t>
+  </si>
+  <si>
+    <t>Salvita Jiménez - Sergio Garrote</t>
+  </si>
+  <si>
+    <t>45,25</t>
+  </si>
+  <si>
+    <t>28,25</t>
+  </si>
+  <si>
+    <t>73,5</t>
+  </si>
+  <si>
+    <t>Pepe Conde - Ángel Torres</t>
+  </si>
+  <si>
+    <t>42,75</t>
+  </si>
+  <si>
+    <t>20,75</t>
+  </si>
+  <si>
+    <t>63,5</t>
+  </si>
+  <si>
+    <t>Adrián Martínez - Jose David</t>
+  </si>
+  <si>
+    <t>76,75</t>
+  </si>
+  <si>
+    <t>Jose Alberto Navarro - Paco Rama</t>
+  </si>
+  <si>
+    <t>43,5</t>
+  </si>
+  <si>
+    <t>Adri Pérez Ibáñez - Antonio Girón</t>
+  </si>
+  <si>
+    <t>56,25</t>
+  </si>
+  <si>
+    <t>17,75</t>
+  </si>
+  <si>
+    <t>Juanele - Javi Granados</t>
+  </si>
+  <si>
+    <t>Pedrito Almansa - Jose Alberto Agenjo</t>
+  </si>
+  <si>
+    <t>57,75</t>
+  </si>
+  <si>
+    <t>22,75</t>
+  </si>
+  <si>
+    <t>80,5</t>
+  </si>
+  <si>
+    <t>Manu Morata - Joel Aguilera</t>
+  </si>
+  <si>
+    <t>58,75</t>
+  </si>
+  <si>
+    <t>Antonio Ballesteros - Luismi</t>
+  </si>
+  <si>
+    <t>39,75</t>
+  </si>
+  <si>
+    <t>79,5</t>
+  </si>
+  <si>
+    <t>Jose Galvez - Alberto López</t>
+  </si>
+  <si>
+    <t>35,25</t>
+  </si>
+  <si>
+    <t>15,5</t>
+  </si>
+  <si>
+    <t>50,75</t>
+  </si>
+  <si>
+    <t>Rafael Castro - Francisco Reca</t>
+  </si>
+  <si>
+    <t>60,25</t>
+  </si>
+  <si>
+    <t>Ramón Ruiz - Gabriel Gálvez</t>
+  </si>
+  <si>
+    <t>74,75</t>
+  </si>
+  <si>
+    <t>Alejandro Ferro - Juan Ferro</t>
+  </si>
+  <si>
+    <t>Alberto Lomas - Juan Carlos Mesa</t>
+  </si>
+  <si>
+    <t>52,25</t>
+  </si>
+  <si>
+    <t>Vanesa Platero - Luis Mena</t>
+  </si>
+  <si>
+    <t>56,75</t>
+  </si>
+  <si>
+    <t>José Manuel Jurado - Ángel Jurado</t>
+  </si>
+  <si>
+    <t>25,75</t>
+  </si>
+  <si>
+    <t>51,5</t>
+  </si>
+  <si>
+    <t>Javier Morón - Manuel Ruiz</t>
+  </si>
+  <si>
+    <t>56,5</t>
+  </si>
+  <si>
+    <t>Anselmo Martínez - Javi Porras</t>
+  </si>
+  <si>
+    <t>18,5</t>
+  </si>
+  <si>
+    <t>José Antonio Sequera - Antonio Luis Peña</t>
+  </si>
+  <si>
+    <t>Pablo Ruiz - Juan Manuel Lloris</t>
+  </si>
+  <si>
+    <t>15,25</t>
+  </si>
+  <si>
+    <t>30,5</t>
+  </si>
+  <si>
+    <t>Manolo Toribio - Raquel Fernández</t>
+  </si>
+  <si>
+    <t>49,25</t>
+  </si>
+  <si>
+    <t>Manuel Moreno - Álvaro López Garcia</t>
+  </si>
+  <si>
+    <t>Emilio Briones Jr - Emilio Briones</t>
+  </si>
+  <si>
+    <t>Manuel Cruz - Javi Barrios</t>
+  </si>
+  <si>
+    <t>17,25</t>
+  </si>
+  <si>
+    <t>5,75</t>
+  </si>
+  <si>
+    <t>Jesús Serra - Sergio Serra</t>
+  </si>
+  <si>
+    <t>22,5</t>
+  </si>
+  <si>
+    <t>31,5</t>
+  </si>
+  <si>
+    <t>Jose Manuel Ibañez - Ángel Villar</t>
+  </si>
+  <si>
+    <t>12,5</t>
+  </si>
+  <si>
+    <t>Ángel Chinchilla - Javier Escribano</t>
+  </si>
+  <si>
+    <t>12,75</t>
+  </si>
+  <si>
+    <t>5,25</t>
+  </si>
+  <si>
+    <t>Alberto Serrano - Jaime Baltanas</t>
+  </si>
+  <si>
+    <t>15,75</t>
+  </si>
+  <si>
+    <t>Paco Hermosilla - Manolo Juárez</t>
+  </si>
+  <si>
+    <t>24,25</t>
+  </si>
+  <si>
+    <t>Sergio Campoy - Isa Monsalve</t>
+  </si>
+  <si>
+    <t>7,5</t>
+  </si>
+  <si>
+    <t>Manu Morata - Maria del Mar Morata</t>
+  </si>
+  <si>
+    <t>34,25</t>
+  </si>
+  <si>
+    <t>Jose Carlos Jiménez - Alejandro Jiménez</t>
+  </si>
+  <si>
+    <t>8,75</t>
+  </si>
+  <si>
+    <t>17,5</t>
+  </si>
+  <si>
+    <t>Agenjo - Estefanía</t>
+  </si>
+  <si>
+    <t>1,25</t>
+  </si>
+  <si>
+    <t>Vanessa Platero - Rocío Muñoz</t>
+  </si>
+  <si>
+    <t>Álvaro Cazorla - Rosa López</t>
+  </si>
+  <si>
+    <t>Jose Alberto Navarro - Sandra Rodríguez</t>
+  </si>
+  <si>
+    <t>16,5</t>
+  </si>
+  <si>
+    <t>Rosa López - Isa Monsalve</t>
+  </si>
+  <si>
+    <t>Antonio Jesús Martos - Fran Otto</t>
+  </si>
+  <si>
+    <t>Laura - Mari Angeles</t>
+  </si>
+  <si>
+    <t>Miguel Angel Arenas - Rafa Robles</t>
+  </si>
+  <si>
+    <t>Miguel Marmol</t>
+  </si>
+  <si>
+    <t>Fernando Cubero</t>
+  </si>
+  <si>
+    <t>Almudena</t>
+  </si>
+  <si>
+    <t>Inma Villacañas</t>
+  </si>
+  <si>
+    <t>Nicanor Hermosilla</t>
+  </si>
+  <si>
+    <t>J. Antonio Berdonces</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,6 +1061,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -662,7 +1093,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -712,17 +1143,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -732,36 +1152,29 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="4"/>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
       </right>
-      <top style="thin">
-        <color theme="4"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
         <color rgb="FFFFFFFF"/>
       </right>
       <top style="medium">
-        <color rgb="FF4F81BD"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
         <color rgb="FFFFFFFF"/>
@@ -776,10 +1189,10 @@
         <color rgb="FFFFFFFF"/>
       </right>
       <top style="medium">
-        <color rgb="FF4F81BD"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -787,12 +1200,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -811,38 +1223,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <b/>
@@ -886,24 +1290,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}" name="Table1" displayName="Table1" ref="A1:H70" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:H70" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H70">
-    <sortCondition ref="A1:A70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}" name="Table1" displayName="Table1" ref="A1:H69" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:H69" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H65">
+    <sortCondition ref="A1:A65"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{F807307C-1923-43CD-9BE6-597899417869}" name="OrdenInicial"/>
     <tableColumn id="2" xr3:uid="{6AF84387-7D32-4414-8CAC-5A560EADBC4A}" name="Division"/>
     <tableColumn id="3" xr3:uid="{84AD3FD4-D92A-4231-887E-3C7BD2E9EBC2}" name="Jugador1"/>
     <tableColumn id="4" xr3:uid="{82CA3A8B-F39B-4BCE-BCC6-304975B679B0}" name="Jugador2"/>
-    <tableColumn id="5" xr3:uid="{94FFF918-49E4-4CD6-ACBA-DF1430BA0582}" name="Pareja" dataDxfId="0">
-      <calculatedColumnFormula>_xlfn.CONCAT(C2," - ",D2)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="5" xr3:uid="{94FFF918-49E4-4CD6-ACBA-DF1430BA0582}" name="Pareja"/>
     <tableColumn id="6" xr3:uid="{A4412226-10DC-49FE-A9BD-51D3566ADADD}" name="Puntos1"/>
     <tableColumn id="7" xr3:uid="{7F2FD959-B902-4327-8ADC-A00D572DB9A9}" name="Puntos2"/>
-    <tableColumn id="8" xr3:uid="{4467FD46-A726-4724-83F0-1290D903BD11}" name="Total">
-      <calculatedColumnFormula>SUM(F2,G2)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="8" xr3:uid="{4467FD46-A726-4724-83F0-1290D903BD11}" name="Total"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1196,44 +1596,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.42578125" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1244,24 +1644,22 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E25" si="0">_xlfn.CONCAT(C2," - ",D2)</f>
-        <v>Grego - Luis Ángel</v>
-      </c>
-      <c r="F2">
-        <v>78.25</v>
-      </c>
-      <c r="G2">
-        <v>78.25</v>
-      </c>
-      <c r="H2">
-        <f t="shared" ref="H2:H25" si="1">SUM(F2,G2)</f>
-        <v>156.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1272,24 +1670,22 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Happy - Pedro Correas</v>
-      </c>
-      <c r="F3">
-        <v>89.75</v>
-      </c>
-      <c r="G3">
-        <v>83.5</v>
-      </c>
-      <c r="H3">
-        <f t="shared" si="1"/>
-        <v>173.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1300,11 +1696,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Junior - Alfonsito</v>
+        <v>68</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="F4">
         <v>125</v>
@@ -1313,11 +1708,10 @@
         <v>125</v>
       </c>
       <c r="H4">
-        <f t="shared" si="1"/>
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1328,24 +1722,22 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Tote - Antonio Gálvez</v>
+        <v>74</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>191</v>
       </c>
       <c r="F5">
         <v>113</v>
       </c>
-      <c r="G5">
-        <v>102.5</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="1"/>
-        <v>215.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1356,24 +1748,22 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Santi Molina - Gusi</v>
-      </c>
-      <c r="F6">
-        <v>85.25</v>
-      </c>
-      <c r="G6">
-        <v>72.25</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="1"/>
-        <v>157.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1384,24 +1774,22 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Manolo Gómez - Joaquín Gea</v>
-      </c>
-      <c r="F7">
-        <v>91.75</v>
-      </c>
-      <c r="G7">
-        <v>91.75</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
-        <v>183.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1412,24 +1800,22 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Jose Ramón - Ramón Piedra</v>
+        <v>72</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="F8">
-        <v>101.625</v>
+        <v>101625</v>
       </c>
       <c r="G8">
-        <v>66.625</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>168.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>66625</v>
+      </c>
+      <c r="H8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1440,444 +1826,412 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Fabián Morata - Raúl Olivetti</v>
+        <v>73</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="F9">
-        <v>83.625</v>
+        <v>83625</v>
       </c>
       <c r="G9">
-        <v>83.125</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
-        <v>166.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>83125</v>
+      </c>
+      <c r="H9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>Albertillo - Marcos Moreno</v>
-      </c>
-      <c r="F10" s="11">
-        <v>76.894999999999996</v>
-      </c>
-      <c r="G10" s="11">
-        <v>50.375</v>
-      </c>
-      <c r="H10" s="12">
-        <f t="shared" si="1"/>
-        <v>127.27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10">
+        <v>76895</v>
+      </c>
+      <c r="G10">
+        <v>50375</v>
+      </c>
+      <c r="H10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>Curro - Julio Carabias</v>
-      </c>
-      <c r="F11" s="11">
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="F11">
         <v>74</v>
       </c>
-      <c r="G11" s="11">
-        <v>53.75</v>
-      </c>
-      <c r="H11" s="12">
-        <f t="shared" si="1"/>
-        <v>127.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>Manuel Choto - Julián</v>
-      </c>
-      <c r="F12" s="11">
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="F12">
         <v>68</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12">
         <v>68</v>
       </c>
-      <c r="H12" s="12">
-        <f t="shared" si="1"/>
+      <c r="H12">
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Álvaro Molina - Jesús Rodrigo</v>
-      </c>
-      <c r="F13" s="11">
-        <v>87.75</v>
-      </c>
-      <c r="G13" s="11">
-        <v>95.375</v>
-      </c>
-      <c r="H13" s="12">
-        <f t="shared" si="1"/>
-        <v>183.125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" t="s">
+        <v>211</v>
+      </c>
+      <c r="G13">
+        <v>95375</v>
+      </c>
+      <c r="H13">
+        <v>183125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14">
         <v>2</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Javi Castillo - Sergio Campoy</v>
-      </c>
-      <c r="F14" s="11">
-        <v>93.25</v>
-      </c>
-      <c r="G14" s="15">
+      <c r="E14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14">
         <v>69</v>
       </c>
-      <c r="H14" s="12">
-        <f t="shared" si="1"/>
-        <v>162.25</v>
+      <c r="H14" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Luis Mena - Carlos Domínguez</v>
-      </c>
-      <c r="F15" s="11">
-        <v>68</v>
-      </c>
-      <c r="G15" s="11">
-        <v>72.375</v>
-      </c>
-      <c r="H15" s="12">
-        <f t="shared" si="1"/>
-        <v>140.375</v>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="F15" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Loren Perea - Manuel Ortega</v>
-      </c>
-      <c r="F16" s="11">
-        <v>55</v>
-      </c>
-      <c r="G16" s="16">
-        <v>59.5</v>
-      </c>
-      <c r="H16" s="12">
-        <f t="shared" si="1"/>
-        <v>114.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17">
         <v>2</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Loren Portillo - Juanmi Sanabria</v>
-      </c>
-      <c r="F17" s="11">
-        <v>92.25</v>
-      </c>
-      <c r="G17" s="11">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12">
-        <f t="shared" si="1"/>
-        <v>92.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F17">
+        <v>59375</v>
+      </c>
+      <c r="G17">
+        <v>34375</v>
+      </c>
+      <c r="H17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18">
         <v>3</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>Fran Collado - Mariano</v>
-      </c>
-      <c r="F18" s="11">
-        <v>70.5</v>
-      </c>
-      <c r="G18" s="11">
-        <v>70.5</v>
-      </c>
-      <c r="H18" s="11">
-        <f t="shared" si="1"/>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G18" t="s">
+        <v>221</v>
+      </c>
+      <c r="H18">
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>Juanjo - Juan Carlos Illescas</v>
-      </c>
-      <c r="F19" s="11">
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19">
         <v>62</v>
       </c>
-      <c r="G19" s="11">
-        <v>33.25</v>
-      </c>
-      <c r="H19" s="11">
-        <f t="shared" si="1"/>
-        <v>95.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>223</v>
+      </c>
+      <c r="H19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20">
         <v>3</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="C20" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Vivi - Juan Sánchez Sr.</v>
-      </c>
-      <c r="F20" s="11">
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F20">
         <v>68</v>
       </c>
-      <c r="G20" s="11">
-        <v>30.25</v>
-      </c>
-      <c r="H20" s="11">
-        <f t="shared" si="1"/>
-        <v>98.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <f t="shared" ref="E21:E24" si="2">_xlfn.CONCAT(C21," - ",D21)</f>
-        <v>Jose Alberto Navarro - Paco Rama</v>
+        <v>151</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="F21">
-        <v>43.5</v>
+        <v>18</v>
       </c>
       <c r="G21">
-        <v>43.5</v>
+        <v>58</v>
       </c>
       <c r="H21">
-        <f t="shared" ref="H21:H24" si="3">SUM(F21,G21)</f>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Adri Pérez Ibáñez - Antonio Girón</v>
+        <v>77</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="F22">
-        <v>56.25</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>17.75</v>
+        <v>66625</v>
       </c>
       <c r="H22">
-        <f t="shared" si="3"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>66625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Pablo Cano - Víctor Ocaña</v>
+        <v>31</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>230</v>
       </c>
       <c r="F23">
-        <v>59.375</v>
+        <v>68</v>
       </c>
       <c r="G23">
-        <v>34.375</v>
+        <v>72375</v>
       </c>
       <c r="H23">
-        <f t="shared" si="3"/>
-        <v>93.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>140375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Juanji - Pedro Utrera</v>
+        <v>94</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="F24">
-        <v>45.875</v>
+        <v>45875</v>
       </c>
       <c r="G24">
-        <v>23.875</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="3"/>
-        <v>69.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23875</v>
+      </c>
+      <c r="H24" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26</v>
       </c>
@@ -1885,27 +2239,25 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>180</v>
-      </c>
-      <c r="E25" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>David Bellido - Manuel Bellido</v>
+        <v>89</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="G25" t="s">
+        <v>234</v>
+      </c>
+      <c r="H25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>27</v>
       </c>
@@ -1916,24 +2268,22 @@
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <f t="shared" ref="E26:E39" si="4">_xlfn.CONCAT(C26," - ",D26)</f>
-        <v>Salvita Jiménez - Sergio Garrote</v>
-      </c>
-      <c r="F26">
-        <v>45.25</v>
-      </c>
-      <c r="G26">
-        <v>28.25</v>
-      </c>
-      <c r="H26">
-        <f t="shared" ref="H26:H39" si="5">SUM(F26,G26)</f>
-        <v>73.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" t="s">
+        <v>237</v>
+      </c>
+      <c r="G26" t="s">
+        <v>238</v>
+      </c>
+      <c r="H26" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>28</v>
       </c>
@@ -1944,24 +2294,22 @@
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Pepe Conde - Ángel Torres</v>
-      </c>
-      <c r="F27">
-        <v>42.75</v>
-      </c>
-      <c r="G27">
-        <v>20.75</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="5"/>
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F27" t="s">
+        <v>241</v>
+      </c>
+      <c r="G27" t="s">
+        <v>242</v>
+      </c>
+      <c r="H27" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>29</v>
       </c>
@@ -1972,108 +2320,100 @@
         <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Adrián Martínez - Jose David</v>
+        <v>98</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>244</v>
       </c>
       <c r="F28">
-        <v>53.125</v>
+        <v>53125</v>
       </c>
       <c r="G28">
-        <v>23.625</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="5"/>
-        <v>76.75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23625</v>
+      </c>
+      <c r="H28" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>30</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>Raúl Garcia - Alvarito</v>
-      </c>
-      <c r="F29" s="11">
-        <v>18</v>
-      </c>
-      <c r="G29" s="11">
-        <v>58</v>
-      </c>
-      <c r="H29" s="12">
-        <f t="shared" si="5"/>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F29" t="s">
+        <v>247</v>
+      </c>
+      <c r="G29" t="s">
+        <v>247</v>
+      </c>
+      <c r="H29">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>31</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>Adrian Camacho - David Hermosilla</v>
-      </c>
-      <c r="F30" s="11">
-        <v>0</v>
-      </c>
-      <c r="G30" s="11">
-        <v>66.625</v>
-      </c>
-      <c r="H30" s="12">
-        <f t="shared" si="5"/>
-        <v>66.625</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="F30" t="s">
+        <v>249</v>
+      </c>
+      <c r="G30" t="s">
+        <v>250</v>
+      </c>
+      <c r="H30">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>32</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>Juanele - Javi Granados</v>
-      </c>
-      <c r="F31" s="11">
-        <v>59.5</v>
-      </c>
-      <c r="G31" s="11">
+      <c r="D31" t="s">
+        <v>168</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="F31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G31">
         <v>0</v>
       </c>
-      <c r="H31" s="12">
-        <f t="shared" si="5"/>
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H31" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>33</v>
       </c>
@@ -2084,24 +2424,22 @@
         <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Pedrito Almansa - Jose Alberto Agenjo</v>
-      </c>
-      <c r="F32">
-        <v>57.75</v>
-      </c>
-      <c r="G32">
-        <v>22.75</v>
-      </c>
-      <c r="H32">
-        <f t="shared" si="5"/>
-        <v>80.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="F32" t="s">
+        <v>253</v>
+      </c>
+      <c r="G32" t="s">
+        <v>254</v>
+      </c>
+      <c r="H32" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>34</v>
       </c>
@@ -2112,24 +2450,22 @@
         <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Manu Morata - Joel Aguilera</v>
+        <v>100</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>256</v>
       </c>
       <c r="F33">
-        <v>41.125</v>
+        <v>41125</v>
       </c>
       <c r="G33">
-        <v>17.625</v>
-      </c>
-      <c r="H33">
-        <f t="shared" si="5"/>
-        <v>58.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17625</v>
+      </c>
+      <c r="H33" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>35</v>
       </c>
@@ -2140,24 +2476,22 @@
         <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Antonio Ballesteros - Luismi</v>
-      </c>
-      <c r="F34">
-        <v>39.75</v>
-      </c>
-      <c r="G34">
-        <v>39.75</v>
-      </c>
-      <c r="H34">
-        <f t="shared" si="5"/>
-        <v>79.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F34" t="s">
+        <v>259</v>
+      </c>
+      <c r="G34" t="s">
+        <v>259</v>
+      </c>
+      <c r="H34" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>36</v>
       </c>
@@ -2168,24 +2502,22 @@
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Jose Galvez - Alberto López</v>
-      </c>
-      <c r="F35">
-        <v>35.25</v>
-      </c>
-      <c r="G35">
-        <v>15.5</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="5"/>
-        <v>50.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F35" t="s">
+        <v>262</v>
+      </c>
+      <c r="G35" t="s">
+        <v>263</v>
+      </c>
+      <c r="H35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>37</v>
       </c>
@@ -2196,24 +2528,22 @@
         <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Rafael Castro - Francisco Reca</v>
+        <v>103</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>265</v>
       </c>
       <c r="F36">
-        <v>30.125</v>
+        <v>30125</v>
       </c>
       <c r="G36">
-        <v>30.125</v>
-      </c>
-      <c r="H36">
-        <f t="shared" si="5"/>
-        <v>60.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>30125</v>
+      </c>
+      <c r="H36" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>38</v>
       </c>
@@ -2224,24 +2554,22 @@
         <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Ramón Ruiz - Gabriel Gálvez</v>
+        <v>105</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>267</v>
       </c>
       <c r="F37">
-        <v>42.875</v>
+        <v>42875</v>
       </c>
       <c r="G37">
-        <v>31.875</v>
-      </c>
-      <c r="H37">
-        <f t="shared" si="5"/>
-        <v>74.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>31875</v>
+      </c>
+      <c r="H37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>39</v>
       </c>
@@ -2252,24 +2580,22 @@
         <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Alejandro Ferro - Juan Ferro</v>
+        <v>106</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>269</v>
       </c>
       <c r="F38">
-        <v>29.875</v>
+        <v>29875</v>
       </c>
       <c r="G38">
-        <v>29.875</v>
-      </c>
-      <c r="H38">
-        <f t="shared" si="5"/>
-        <v>59.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29875</v>
+      </c>
+      <c r="H38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>40</v>
       </c>
@@ -2280,24 +2606,22 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Alberto Lomas - Juan Carlos Mesa</v>
+        <v>107</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="F39">
-        <v>34.125</v>
+        <v>34125</v>
       </c>
       <c r="G39">
-        <v>18.125</v>
-      </c>
-      <c r="H39">
-        <f t="shared" si="5"/>
-        <v>52.25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18125</v>
+      </c>
+      <c r="H39" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>41</v>
       </c>
@@ -2310,22 +2634,20 @@
       <c r="D40" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="2" t="str">
-        <f t="shared" ref="E40:E65" si="6">_xlfn.CONCAT(C40," - ",D40)</f>
-        <v>Vanesa Platero - Luis Mena</v>
+      <c r="E40" s="11" t="s">
+        <v>272</v>
       </c>
       <c r="F40">
-        <v>28.375</v>
+        <v>28375</v>
       </c>
       <c r="G40">
-        <v>28.375</v>
-      </c>
-      <c r="H40">
-        <f t="shared" ref="H40:H65" si="7">SUM(F40,G40)</f>
-        <v>56.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>28375</v>
+      </c>
+      <c r="H40" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>42</v>
       </c>
@@ -2336,24 +2658,22 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>José Manuel Jurado - Ángel Jurado</v>
-      </c>
-      <c r="F41">
-        <v>25.75</v>
-      </c>
-      <c r="G41">
-        <v>25.75</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="7"/>
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F41" t="s">
+        <v>275</v>
+      </c>
+      <c r="G41" t="s">
+        <v>275</v>
+      </c>
+      <c r="H41" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>43</v>
       </c>
@@ -2364,24 +2684,22 @@
         <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <f t="shared" ref="E42:E48" si="8">_xlfn.CONCAT(C42," - ",D42)</f>
-        <v>Javier Morón - Manuel Ruiz</v>
-      </c>
-      <c r="F42">
-        <v>28.25</v>
-      </c>
-      <c r="G42">
-        <v>28.25</v>
-      </c>
-      <c r="H42">
-        <f t="shared" ref="H42:H48" si="9">SUM(F42,G42)</f>
-        <v>56.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="F42" t="s">
+        <v>238</v>
+      </c>
+      <c r="G42" t="s">
+        <v>238</v>
+      </c>
+      <c r="H42" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>44</v>
       </c>
@@ -2392,24 +2710,22 @@
         <v>51</v>
       </c>
       <c r="D43" t="s">
-        <v>111</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Anselmo Martínez - Javi Porras</v>
-      </c>
-      <c r="F43">
-        <v>18.5</v>
-      </c>
-      <c r="G43">
-        <v>18.5</v>
+        <v>110</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F43" t="s">
+        <v>280</v>
+      </c>
+      <c r="G43" t="s">
+        <v>280</v>
       </c>
       <c r="H43">
-        <f t="shared" si="9"/>
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>45</v>
       </c>
@@ -2420,24 +2736,22 @@
         <v>52</v>
       </c>
       <c r="D44" t="s">
-        <v>112</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>José Antonio Sequera - Antonio Luis Peña</v>
+        <v>111</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>281</v>
       </c>
       <c r="F44">
-        <v>26.125</v>
+        <v>26125</v>
       </c>
       <c r="G44">
-        <v>26.125</v>
-      </c>
-      <c r="H44">
-        <f t="shared" si="9"/>
-        <v>52.25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>26125</v>
+      </c>
+      <c r="H44" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>46</v>
       </c>
@@ -2448,24 +2762,22 @@
         <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Pablo Ruiz - Juan Manuel Lloris</v>
-      </c>
-      <c r="F45">
-        <v>15.25</v>
-      </c>
-      <c r="G45">
-        <v>15.25</v>
-      </c>
-      <c r="H45">
-        <f t="shared" si="9"/>
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="F45" t="s">
+        <v>283</v>
+      </c>
+      <c r="G45" t="s">
+        <v>283</v>
+      </c>
+      <c r="H45" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>47</v>
       </c>
@@ -2476,80 +2788,74 @@
         <v>54</v>
       </c>
       <c r="D46" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Manolo Toribio - Raquel Fernández</v>
+        <v>113</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="F46">
-        <v>24.625</v>
+        <v>24625</v>
       </c>
       <c r="G46">
-        <v>24.625</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="9"/>
-        <v>49.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>24625</v>
+      </c>
+      <c r="H46" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E47" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v>Manuel Moreno - Álvaro López Garcia</v>
-      </c>
-      <c r="F47" s="11">
+      <c r="C47" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" t="s">
+        <v>120</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F47">
         <v>29</v>
       </c>
-      <c r="G47" s="11">
-        <v>6.125</v>
-      </c>
-      <c r="H47" s="12">
-        <f t="shared" si="9"/>
-        <v>35.125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G47">
+        <v>6125</v>
+      </c>
+      <c r="H47">
+        <v>35125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>49</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E48" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v>Emilio Briones Jr - Emilio Briones</v>
-      </c>
-      <c r="F48" s="11">
+      <c r="C48" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48">
         <v>0</v>
       </c>
-      <c r="G48" s="11">
-        <v>20.875</v>
-      </c>
-      <c r="H48" s="12">
-        <f t="shared" si="9"/>
-        <v>20.875</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G48">
+        <v>20875</v>
+      </c>
+      <c r="H48">
+        <v>20875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>50</v>
       </c>
@@ -2560,24 +2866,22 @@
         <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>115</v>
-      </c>
-      <c r="E49" t="str">
-        <f t="shared" si="6"/>
-        <v>Manuel Cruz - Javi Barrios</v>
-      </c>
-      <c r="F49">
-        <v>17.25</v>
-      </c>
-      <c r="G49">
-        <v>5.75</v>
+        <v>114</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="F49" t="s">
+        <v>290</v>
+      </c>
+      <c r="G49" t="s">
+        <v>291</v>
       </c>
       <c r="H49">
-        <f t="shared" si="7"/>
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>51</v>
       </c>
@@ -2588,24 +2892,22 @@
         <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>116</v>
-      </c>
-      <c r="E50" t="str">
-        <f t="shared" si="6"/>
-        <v>Luis Medina - Ray Jiménez</v>
-      </c>
-      <c r="F50">
-        <v>22.375</v>
+        <v>115</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="F50" t="s">
+        <v>293</v>
       </c>
       <c r="G50">
-        <v>17.875</v>
-      </c>
-      <c r="H50">
-        <f t="shared" si="7"/>
-        <v>40.25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H50" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>52</v>
       </c>
@@ -2616,24 +2918,22 @@
         <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>117</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Jesús Serra - Sergio Serra</v>
-      </c>
-      <c r="F51">
-        <v>22.5</v>
-      </c>
-      <c r="G51">
-        <v>9</v>
+        <v>116</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="F51" t="s">
+        <v>296</v>
+      </c>
+      <c r="G51" t="s">
+        <v>296</v>
       </c>
       <c r="H51">
-        <f t="shared" si="7"/>
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>53</v>
       </c>
@@ -2644,24 +2944,22 @@
         <v>58</v>
       </c>
       <c r="D52" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Jose Manuel Ibañez - Ángel Villar</v>
-      </c>
-      <c r="F52">
-        <v>12.5</v>
-      </c>
-      <c r="G52">
-        <v>12.5</v>
+        <v>117</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="F52" t="s">
+        <v>298</v>
+      </c>
+      <c r="G52" t="s">
+        <v>299</v>
       </c>
       <c r="H52">
-        <f t="shared" si="7"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>54</v>
       </c>
@@ -2672,24 +2970,22 @@
         <v>59</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Ángel Chinchilla - Javier Escribano</v>
-      </c>
-      <c r="F53">
-        <v>12.75</v>
-      </c>
-      <c r="G53">
-        <v>5.25</v>
-      </c>
-      <c r="H53">
-        <f t="shared" si="7"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="F53" t="s">
+        <v>301</v>
+      </c>
+      <c r="G53" t="s">
+        <v>301</v>
+      </c>
+      <c r="H53" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>55</v>
       </c>
@@ -2700,24 +2996,22 @@
         <v>60</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Alberto Serrano - Jaime Baltanas</v>
+        <v>119</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>302</v>
       </c>
       <c r="F54">
-        <v>15.75</v>
+        <v>12125</v>
       </c>
       <c r="G54">
-        <v>15.75</v>
-      </c>
-      <c r="H54">
-        <f t="shared" si="7"/>
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>12125</v>
+      </c>
+      <c r="H54" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>56</v>
       </c>
@@ -2725,27 +3019,25 @@
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D55" t="s">
         <v>121</v>
       </c>
-      <c r="E55" t="str">
-        <f t="shared" si="6"/>
-        <v>Paco Hermosilla - Manolo Juárez</v>
-      </c>
-      <c r="F55">
-        <v>12.125</v>
+      <c r="E55" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="F55" t="s">
+        <v>305</v>
       </c>
       <c r="G55">
-        <v>12.125</v>
+        <v>18125</v>
       </c>
       <c r="H55">
-        <f t="shared" si="7"/>
-        <v>24.25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>25625</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>57</v>
       </c>
@@ -2753,27 +3045,25 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D56" t="s">
         <v>123</v>
       </c>
-      <c r="E56" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Sergio Campoy - Isa Monsalve</v>
+      <c r="E56" s="11" t="s">
+        <v>306</v>
       </c>
       <c r="F56">
-        <v>7.5</v>
+        <v>17125</v>
       </c>
       <c r="G56">
-        <v>18.125</v>
-      </c>
-      <c r="H56">
-        <f t="shared" si="7"/>
-        <v>25.625</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17125</v>
+      </c>
+      <c r="H56" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>58</v>
       </c>
@@ -2781,27 +3071,25 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Manu Morata - Maria del Mar Morata</v>
-      </c>
-      <c r="F57">
-        <v>17.125</v>
-      </c>
-      <c r="G57">
-        <v>17.125</v>
-      </c>
-      <c r="H57">
-        <f t="shared" si="7"/>
-        <v>34.25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="F57" t="s">
+        <v>309</v>
+      </c>
+      <c r="G57" t="s">
+        <v>309</v>
+      </c>
+      <c r="H57" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>59</v>
       </c>
@@ -2809,55 +3097,51 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>171</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Jose Carlos Jiménez - Alejandro Jiménez</v>
+        <v>122</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="F58">
-        <v>8.75</v>
-      </c>
-      <c r="G58">
-        <v>8.75</v>
-      </c>
-      <c r="H58">
-        <f t="shared" si="7"/>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>312</v>
+      </c>
+      <c r="H58" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59">
         <v>8</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E59" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>Agenjo - Estefanía</v>
-      </c>
-      <c r="F59" s="11">
-        <v>0</v>
-      </c>
-      <c r="G59" s="11">
-        <v>1.25</v>
+      <c r="C59" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" t="s">
+        <v>125</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="F59" t="s">
+        <v>305</v>
+      </c>
+      <c r="G59" t="s">
+        <v>305</v>
       </c>
       <c r="H59">
-        <f t="shared" si="7"/>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>61</v>
       </c>
@@ -2868,24 +3152,22 @@
         <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Vanessa Platero - Rocío Muñoz</v>
+        <v>65</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>314</v>
       </c>
       <c r="F60">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="G60">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="H60">
-        <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>62</v>
       </c>
@@ -2893,27 +3175,25 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>66</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Álvaro Cazorla - Rosa López</v>
+        <v>126</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>315</v>
       </c>
       <c r="F61">
-        <v>11</v>
+        <v>8875</v>
       </c>
       <c r="G61">
-        <v>11</v>
-      </c>
-      <c r="H61">
-        <f t="shared" si="7"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>7625</v>
+      </c>
+      <c r="H61" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>63</v>
       </c>
@@ -2921,24 +3201,22 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Jose Alberto Navarro - Sandra Rodríguez</v>
+        <v>121</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="F62">
-        <v>8.875</v>
+        <v>11125</v>
       </c>
       <c r="G62">
-        <v>7.625</v>
+        <v>14875</v>
       </c>
       <c r="H62">
-        <f t="shared" si="7"/>
-        <v>16.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2949,24 +3227,22 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="D63" t="s">
-        <v>123</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Rosa López - Isa Monsalve</v>
+        <v>173</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>318</v>
       </c>
       <c r="F63">
-        <v>11.125</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>14.875</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2976,15 +3252,14 @@
       <c r="B64">
         <v>8</v>
       </c>
-      <c r="C64" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <f>_xlfn.CONCAT(C64," - ",D64)</f>
-        <v>Laura - Mari Angeles</v>
+      <c r="C64" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" t="s">
+        <v>180</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>319</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2993,26 +3268,24 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>66</v>
       </c>
       <c r="B65">
         <v>8</v>
       </c>
-      <c r="C65" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E65" s="9" t="str">
-        <f t="shared" ref="E65" si="10">_xlfn.CONCAT(C65," - ",D65)</f>
-        <v>Antonio Jesús Martos - Fran Otto</v>
+      <c r="C65" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>320</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3021,11 +3294,10 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <f t="shared" ref="H65" si="11">SUM(F65,G65)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>67</v>
       </c>
@@ -3033,14 +3305,14 @@
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>183</v>
+        <v>321</v>
       </c>
       <c r="D66" t="s">
-        <v>184</v>
-      </c>
-      <c r="E66" s="11" t="str">
-        <f t="shared" ref="E66:E70" si="12">_xlfn.CONCAT(C66," - ",D66)</f>
-        <v>Miguel Angel Arenas - Rafa Robles</v>
+        <v>322</v>
+      </c>
+      <c r="E66" s="12" t="str">
+        <f>CONCATENATE(Table1[[#This Row],[Jugador1]]," - ",Table1[[#This Row],[Jugador2]])</f>
+        <v>Miguel Marmol - Fernando Cubero</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3049,78 +3321,69 @@
         <v>0</v>
       </c>
       <c r="H66">
-        <f t="shared" ref="H66:H70" si="13">SUM(F66,G66)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>68</v>
       </c>
       <c r="B67">
         <v>9</v>
       </c>
-      <c r="E67" s="11" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> - </v>
+      <c r="C67" t="s">
+        <v>323</v>
+      </c>
+      <c r="D67" t="s">
+        <v>324</v>
+      </c>
+      <c r="E67" s="12" t="str">
+        <f>CONCATENATE(Table1[[#This Row],[Jugador1]]," - ",Table1[[#This Row],[Jugador2]])</f>
+        <v>Almudena - Inma Villacañas</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
       </c>
       <c r="H67">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>69</v>
       </c>
       <c r="B68">
         <v>9</v>
       </c>
-      <c r="E68" s="11" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> - </v>
+      <c r="C68" t="s">
+        <v>325</v>
+      </c>
+      <c r="D68" t="s">
+        <v>326</v>
+      </c>
+      <c r="E68" s="12" t="str">
+        <f>CONCATENATE(Table1[[#This Row],[Jugador1]]," - ",Table1[[#This Row],[Jugador2]])</f>
+        <v>Nicanor Hermosilla - J. Antonio Berdonces</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
       </c>
       <c r="H68">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>70</v>
-      </c>
-      <c r="B69">
-        <v>9</v>
-      </c>
-      <c r="E69" s="11" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="H69">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>71</v>
-      </c>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="11" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="H70">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3135,264 +3398,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B5" s="5">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="6">
-        <v>27</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="B8" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="6" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C10" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="5">
+        <v>55</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="5">
+        <v>69</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="6">
+        <v>3875</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="6">
+        <v>3875</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="5">
+        <v>58</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="5">
         <v>68</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="6">
-        <v>55</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="6">
-        <v>69</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="7">
-        <v>3875</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="7">
-        <v>3875</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="6">
-        <v>58</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="6">
-        <v>68</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="6" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="B18" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="B20" s="6">
+        <v>80625</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="7">
-        <v>80625</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B21" s="5">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B22" s="5">
         <v>17</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C22" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="B23" s="6">
+        <v>19375</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B22" s="6">
-        <v>17</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" s="7">
-        <v>19375</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B24" s="7">
+      <c r="B24" s="6">
         <v>39875</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>139</v>
+      <c r="C24" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>77</v>
+      <c r="A25" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="B25">
         <v>38.25</v>
@@ -3400,7 +3663,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26">
         <v>58.5</v>
@@ -3416,7 +3679,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28">
         <v>6.125</v>
@@ -3432,46 +3695,46 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B30">
         <v>34.5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" s="11">
+      <c r="A31" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="8">
         <v>40.875</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B32">
         <v>19.5</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>80</v>
+      <c r="A33" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="B33">
         <v>40.75</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>70</v>
+      <c r="A34" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="B34">
         <v>82.25</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B35">
@@ -3480,14 +3743,14 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36">
         <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B37">
@@ -3496,7 +3759,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38">
         <v>67.5</v>

--- a/sources/02032026/Liga2026-ParejasIniciales-Provisional.xlsx
+++ b/sources/02032026/Liga2026-ParejasIniciales-Provisional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hermosil\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF1C412-4DC9-43D2-A1A7-C278197133B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74FE2D0-FB5B-43FA-BA2E-57B43BB9313C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31920" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parejas" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="322">
   <si>
     <t>Division</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Fabián Morata</t>
   </si>
   <si>
-    <t>Tote</t>
-  </si>
-  <si>
     <t>Álvaro Molina</t>
   </si>
   <si>
@@ -258,9 +255,6 @@
     <t>Raúl Olivetti</t>
   </si>
   <si>
-    <t>Antonio Gálvez</t>
-  </si>
-  <si>
     <t>Marcos Moreno</t>
   </si>
   <si>
@@ -607,15 +601,6 @@
   </si>
   <si>
     <t>Junior - Alfonsito</t>
-  </si>
-  <si>
-    <t>Tote - Antonio Gálvez</t>
-  </si>
-  <si>
-    <t>102,5</t>
-  </si>
-  <si>
-    <t>215,5</t>
   </si>
   <si>
     <t>Santi Molina - Gusi</t>
@@ -1290,10 +1275,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}" name="Table1" displayName="Table1" ref="A1:H69" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:H69" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H65">
-    <sortCondition ref="A1:A65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}" name="Table1" displayName="Table1" ref="A1:H68" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:H68" xr:uid="{981F46C5-E7F8-4EC6-BC04-13FC046E9002}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H64">
+    <sortCondition ref="A1:A64"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{F807307C-1923-43CD-9BE6-597899417869}" name="OrdenInicial"/>
@@ -1596,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1609,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1630,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1644,19 +1629,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" t="s">
         <v>183</v>
-      </c>
-      <c r="F2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1670,19 +1655,19 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G3" t="s">
         <v>186</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>187</v>
-      </c>
-      <c r="G3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1696,10 +1681,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F4">
         <v>125</v>
@@ -1719,22 +1704,22 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" t="s">
+        <v>190</v>
+      </c>
+      <c r="G5" t="s">
         <v>191</v>
       </c>
-      <c r="F5">
-        <v>113</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>192</v>
-      </c>
-      <c r="H5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1745,22 +1730,22 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>70</v>
       </c>
       <c r="E6" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" t="s">
         <v>194</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H6" t="s">
         <v>195</v>
-      </c>
-      <c r="G6" t="s">
-        <v>196</v>
-      </c>
-      <c r="H6" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1771,22 +1756,22 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" t="s">
-        <v>199</v>
-      </c>
-      <c r="G7" t="s">
-        <v>199</v>
+        <v>196</v>
+      </c>
+      <c r="F7">
+        <v>101625</v>
+      </c>
+      <c r="G7">
+        <v>66625</v>
       </c>
       <c r="H7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1797,22 +1782,22 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
         <v>72</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F8">
-        <v>101625</v>
+        <v>83625</v>
       </c>
       <c r="G8">
-        <v>66625</v>
+        <v>83125</v>
       </c>
       <c r="H8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1823,22 +1808,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>73</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F9">
-        <v>83625</v>
+        <v>76895</v>
       </c>
       <c r="G9">
-        <v>83125</v>
+        <v>50375</v>
       </c>
       <c r="H9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1849,22 +1834,22 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F10">
-        <v>76895</v>
-      </c>
-      <c r="G10">
-        <v>50375</v>
+        <v>74</v>
+      </c>
+      <c r="G10" t="s">
+        <v>131</v>
       </c>
       <c r="H10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1875,22 +1860,22 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>78</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F11">
-        <v>74</v>
-      </c>
-      <c r="G11" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" t="s">
-        <v>208</v>
+        <v>68</v>
+      </c>
+      <c r="G11">
+        <v>68</v>
+      </c>
+      <c r="H11">
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1901,22 +1886,22 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12">
-        <v>68</v>
+      <c r="E12" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F12" t="s">
+        <v>206</v>
       </c>
       <c r="G12">
-        <v>68</v>
+        <v>95375</v>
       </c>
       <c r="H12">
-        <v>136</v>
+        <v>183125</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1927,22 +1912,22 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F13" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G13">
-        <v>95375</v>
-      </c>
-      <c r="H13">
-        <v>183125</v>
+        <v>69</v>
+      </c>
+      <c r="H13" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1953,22 +1938,22 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G14">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1979,22 +1964,22 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="F15" t="s">
-        <v>216</v>
+        <v>212</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" t="s">
-        <v>216</v>
+      <c r="H15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2005,22 +1990,22 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>217</v>
+        <v>91</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>59375</v>
       </c>
       <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+        <v>34375</v>
+      </c>
+      <c r="H16" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2031,22 +2016,22 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="F17">
-        <v>59375</v>
-      </c>
-      <c r="G17">
-        <v>34375</v>
-      </c>
-      <c r="H17" t="s">
-        <v>219</v>
+        <v>215</v>
+      </c>
+      <c r="F17" t="s">
+        <v>216</v>
+      </c>
+      <c r="G17" t="s">
+        <v>216</v>
+      </c>
+      <c r="H17">
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2060,206 +2045,206 @@
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="F18" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="F18">
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>221</v>
-      </c>
-      <c r="H18">
-        <v>141</v>
+        <v>218</v>
+      </c>
+      <c r="H18" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19">
+        <v>68</v>
+      </c>
+      <c r="G19" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" t="s">
         <v>222</v>
-      </c>
-      <c r="F19">
-        <v>62</v>
-      </c>
-      <c r="G19" t="s">
-        <v>223</v>
-      </c>
-      <c r="H19" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F20">
-        <v>68</v>
-      </c>
-      <c r="G20" t="s">
-        <v>226</v>
-      </c>
-      <c r="H20" t="s">
-        <v>227</v>
+        <v>18</v>
+      </c>
+      <c r="G20">
+        <v>58</v>
+      </c>
+      <c r="H20">
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>58</v>
+        <v>66625</v>
       </c>
       <c r="H21">
-        <v>76</v>
+        <v>66625</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G22">
-        <v>66625</v>
+        <v>72375</v>
       </c>
       <c r="H22">
-        <v>66625</v>
+        <v>140375</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>230</v>
+        <v>92</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="F23">
-        <v>68</v>
+        <v>45875</v>
       </c>
       <c r="G23">
-        <v>72375</v>
-      </c>
-      <c r="H23">
-        <v>140375</v>
+        <v>23875</v>
+      </c>
+      <c r="H23" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>231</v>
+        <v>87</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="F24">
-        <v>45875</v>
-      </c>
-      <c r="G24">
-        <v>23875</v>
+        <v>55</v>
+      </c>
+      <c r="G24" t="s">
+        <v>229</v>
       </c>
       <c r="H24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F25" t="s">
+        <v>232</v>
+      </c>
+      <c r="G25" t="s">
         <v>233</v>
       </c>
-      <c r="F25">
-        <v>55</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>234</v>
-      </c>
-      <c r="H25" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -2268,154 +2253,154 @@
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E26" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" t="s">
         <v>236</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>237</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>238</v>
-      </c>
-      <c r="H26" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
         <v>96</v>
       </c>
       <c r="E27" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="F27">
+        <v>53125</v>
+      </c>
+      <c r="G27">
+        <v>23625</v>
+      </c>
+      <c r="H27" t="s">
         <v>240</v>
-      </c>
-      <c r="F27" t="s">
-        <v>241</v>
-      </c>
-      <c r="G27" t="s">
-        <v>242</v>
-      </c>
-      <c r="H27" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="F28">
-        <v>53125</v>
-      </c>
-      <c r="G28">
-        <v>23625</v>
-      </c>
-      <c r="H28" t="s">
-        <v>245</v>
+        <v>241</v>
+      </c>
+      <c r="F28" t="s">
+        <v>242</v>
+      </c>
+      <c r="G28" t="s">
+        <v>242</v>
+      </c>
+      <c r="H28">
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
         <v>90</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F29" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H29">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>248</v>
+        <v>166</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="F30" t="s">
-        <v>249</v>
-      </c>
-      <c r="G30" t="s">
-        <v>250</v>
-      </c>
-      <c r="H30">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>251</v>
+        <v>97</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>247</v>
       </c>
       <c r="F31" t="s">
-        <v>234</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
+        <v>248</v>
+      </c>
+      <c r="G31" t="s">
+        <v>249</v>
       </c>
       <c r="H31" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -2424,24 +2409,24 @@
         <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="F32">
+        <v>41125</v>
+      </c>
+      <c r="G32">
+        <v>17625</v>
+      </c>
+      <c r="H32" t="s">
         <v>252</v>
-      </c>
-      <c r="F32" t="s">
-        <v>253</v>
-      </c>
-      <c r="G32" t="s">
-        <v>254</v>
-      </c>
-      <c r="H32" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>4</v>
@@ -2450,24 +2435,24 @@
         <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="F33">
-        <v>41125</v>
-      </c>
-      <c r="G33">
-        <v>17625</v>
+        <v>253</v>
+      </c>
+      <c r="F33" t="s">
+        <v>254</v>
+      </c>
+      <c r="G33" t="s">
+        <v>254</v>
       </c>
       <c r="H33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -2476,24 +2461,24 @@
         <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E34" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F34" t="s">
+        <v>257</v>
+      </c>
+      <c r="G34" t="s">
         <v>258</v>
       </c>
-      <c r="F34" t="s">
+      <c r="H34" t="s">
         <v>259</v>
-      </c>
-      <c r="G34" t="s">
-        <v>259</v>
-      </c>
-      <c r="H34" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -2502,50 +2487,50 @@
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F35">
+        <v>30125</v>
+      </c>
+      <c r="G35">
+        <v>30125</v>
+      </c>
+      <c r="H35" t="s">
         <v>261</v>
-      </c>
-      <c r="F35" t="s">
-        <v>262</v>
-      </c>
-      <c r="G35" t="s">
-        <v>263</v>
-      </c>
-      <c r="H35" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
         <v>103</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F36">
-        <v>30125</v>
+        <v>42875</v>
       </c>
       <c r="G36">
-        <v>30125</v>
+        <v>31875</v>
       </c>
       <c r="H36" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -2554,24 +2539,24 @@
         <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F37">
-        <v>42875</v>
+        <v>29875</v>
       </c>
       <c r="G37">
-        <v>31875</v>
+        <v>29875</v>
       </c>
       <c r="H37" t="s">
-        <v>268</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -2580,24 +2565,24 @@
         <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F38">
-        <v>29875</v>
+        <v>34125</v>
       </c>
       <c r="G38">
-        <v>29875</v>
+        <v>18125</v>
       </c>
       <c r="H38" t="s">
-        <v>159</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -2606,24 +2591,24 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F39">
-        <v>34125</v>
+        <v>28375</v>
       </c>
       <c r="G39">
-        <v>18125</v>
+        <v>28375</v>
       </c>
       <c r="H39" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -2632,24 +2617,24 @@
         <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="F40">
-        <v>28375</v>
-      </c>
-      <c r="G40">
-        <v>28375</v>
+        <v>269</v>
+      </c>
+      <c r="F40" t="s">
+        <v>270</v>
+      </c>
+      <c r="G40" t="s">
+        <v>270</v>
       </c>
       <c r="H40" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -2658,24 +2643,24 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F41" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="G41" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="H41" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -2684,24 +2669,24 @@
         <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F42" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="G42" t="s">
-        <v>238</v>
-      </c>
-      <c r="H42" t="s">
-        <v>278</v>
+        <v>275</v>
+      </c>
+      <c r="H42">
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43">
         <v>6</v>
@@ -2710,24 +2695,24 @@
         <v>51</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="F43" t="s">
-        <v>280</v>
-      </c>
-      <c r="G43" t="s">
-        <v>280</v>
-      </c>
-      <c r="H43">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="F43">
+        <v>26125</v>
+      </c>
+      <c r="G43">
+        <v>26125</v>
+      </c>
+      <c r="H43" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -2736,24 +2721,24 @@
         <v>52</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="F44">
-        <v>26125</v>
-      </c>
-      <c r="G44">
-        <v>26125</v>
+        <v>277</v>
+      </c>
+      <c r="F44" t="s">
+        <v>278</v>
+      </c>
+      <c r="G44" t="s">
+        <v>278</v>
       </c>
       <c r="H44" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45">
         <v>6</v>
@@ -2762,102 +2747,102 @@
         <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="F45" t="s">
-        <v>283</v>
-      </c>
-      <c r="G45" t="s">
-        <v>283</v>
+        <v>280</v>
+      </c>
+      <c r="F45">
+        <v>24625</v>
+      </c>
+      <c r="G45">
+        <v>24625</v>
       </c>
       <c r="H45" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>285</v>
+        <v>118</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>282</v>
       </c>
       <c r="F46">
-        <v>24625</v>
+        <v>29</v>
       </c>
       <c r="G46">
-        <v>24625</v>
-      </c>
-      <c r="H46" t="s">
-        <v>286</v>
+        <v>6125</v>
+      </c>
+      <c r="H46">
+        <v>35125</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>287</v>
+        <v>89</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>283</v>
       </c>
       <c r="F47">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>6125</v>
+        <v>20875</v>
       </c>
       <c r="H47">
-        <v>35125</v>
+        <v>20875</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>20875</v>
+        <v>112</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F48" t="s">
+        <v>285</v>
+      </c>
+      <c r="G48" t="s">
+        <v>286</v>
       </c>
       <c r="H48">
-        <v>20875</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -2866,24 +2851,24 @@
         <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="F49" t="s">
+        <v>288</v>
+      </c>
+      <c r="G49">
+        <v>9</v>
+      </c>
+      <c r="H49" t="s">
         <v>289</v>
-      </c>
-      <c r="F49" t="s">
-        <v>290</v>
-      </c>
-      <c r="G49" t="s">
-        <v>291</v>
-      </c>
-      <c r="H49">
-        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50">
         <v>7</v>
@@ -2892,24 +2877,24 @@
         <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F50" t="s">
-        <v>293</v>
-      </c>
-      <c r="G50">
-        <v>9</v>
-      </c>
-      <c r="H50" t="s">
-        <v>294</v>
+        <v>291</v>
+      </c>
+      <c r="G50" t="s">
+        <v>291</v>
+      </c>
+      <c r="H50">
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B51">
         <v>7</v>
@@ -2918,24 +2903,24 @@
         <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F51" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G51" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H51">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B52">
         <v>7</v>
@@ -2944,24 +2929,24 @@
         <v>58</v>
       </c>
       <c r="D52" t="s">
-        <v>117</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>297</v>
+        <v>116</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="F52" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G52" t="s">
-        <v>299</v>
-      </c>
-      <c r="H52">
-        <v>18</v>
+        <v>296</v>
+      </c>
+      <c r="H52" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53">
         <v>7</v>
@@ -2970,154 +2955,154 @@
         <v>59</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="F53" t="s">
-        <v>301</v>
-      </c>
-      <c r="G53" t="s">
-        <v>301</v>
+        <v>117</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F53">
+        <v>12125</v>
+      </c>
+      <c r="G53">
+        <v>12125</v>
       </c>
       <c r="H53" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54">
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D54" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="F54">
-        <v>12125</v>
+      <c r="E54" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="F54" t="s">
+        <v>300</v>
       </c>
       <c r="G54">
-        <v>12125</v>
-      </c>
-      <c r="H54" t="s">
-        <v>303</v>
+        <v>18125</v>
+      </c>
+      <c r="H54">
+        <v>25625</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B55">
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D55" t="s">
         <v>121</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="F55" t="s">
-        <v>305</v>
+        <v>301</v>
+      </c>
+      <c r="F55">
+        <v>17125</v>
       </c>
       <c r="G55">
-        <v>18125</v>
-      </c>
-      <c r="H55">
-        <v>25625</v>
+        <v>17125</v>
+      </c>
+      <c r="H55" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B56">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="F56">
-        <v>17125</v>
-      </c>
-      <c r="G56">
-        <v>17125</v>
+        <v>303</v>
+      </c>
+      <c r="F56" t="s">
+        <v>304</v>
+      </c>
+      <c r="G56" t="s">
+        <v>304</v>
       </c>
       <c r="H56" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B57">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="F57" t="s">
-        <v>309</v>
+        <v>120</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H57" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B58">
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>171</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
-        <v>122</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="F58" t="s">
+        <v>300</v>
       </c>
       <c r="G58" t="s">
-        <v>312</v>
-      </c>
-      <c r="H58" t="s">
-        <v>312</v>
+        <v>300</v>
+      </c>
+      <c r="H58">
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B59">
         <v>8</v>
@@ -3126,114 +3111,114 @@
         <v>63</v>
       </c>
       <c r="D59" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="F59" t="s">
-        <v>305</v>
-      </c>
-      <c r="G59" t="s">
-        <v>305</v>
+        <v>309</v>
+      </c>
+      <c r="F59">
+        <v>11</v>
+      </c>
+      <c r="G59">
+        <v>11</v>
       </c>
       <c r="H59">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B60">
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D60" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F60">
-        <v>11</v>
+        <v>8875</v>
       </c>
       <c r="G60">
-        <v>11</v>
-      </c>
-      <c r="H60">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7625</v>
+      </c>
+      <c r="H60" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B61">
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F61">
-        <v>8875</v>
+        <v>11125</v>
       </c>
       <c r="G61">
-        <v>7625</v>
-      </c>
-      <c r="H61" t="s">
-        <v>316</v>
+        <v>14875</v>
+      </c>
+      <c r="H61">
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B62">
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="D62" t="s">
-        <v>121</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>317</v>
+        <v>171</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>313</v>
       </c>
       <c r="F62">
-        <v>11125</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>14875</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B63">
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D63" t="s">
-        <v>173</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>318</v>
+        <v>178</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>314</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3247,7 +3232,7 @@
     </row>
     <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B64">
         <v>8</v>
@@ -3258,8 +3243,8 @@
       <c r="D64" t="s">
         <v>180</v>
       </c>
-      <c r="E64" s="11" t="s">
-        <v>319</v>
+      <c r="E64" s="12" t="s">
+        <v>315</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3273,19 +3258,20 @@
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B65">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>181</v>
+        <v>316</v>
       </c>
       <c r="D65" t="s">
-        <v>182</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>320</v>
+        <v>317</v>
+      </c>
+      <c r="E65" s="12" t="str">
+        <f>CONCATENATE(Table1[[#This Row],[Jugador1]]," - ",Table1[[#This Row],[Jugador2]])</f>
+        <v>Miguel Marmol - Fernando Cubero</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3299,20 +3285,20 @@
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B66">
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D66" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E66" s="12" t="str">
         <f>CONCATENATE(Table1[[#This Row],[Jugador1]]," - ",Table1[[#This Row],[Jugador2]])</f>
-        <v>Miguel Marmol - Fernando Cubero</v>
+        <v>Almudena - Inma Villacañas</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3326,20 +3312,20 @@
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B67">
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E67" s="12" t="str">
         <f>CONCATENATE(Table1[[#This Row],[Jugador1]]," - ",Table1[[#This Row],[Jugador2]])</f>
-        <v>Almudena - Inma Villacañas</v>
+        <v>Nicanor Hermosilla - J. Antonio Berdonces</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3348,33 +3334,6 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>69</v>
-      </c>
-      <c r="B68">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>325</v>
-      </c>
-      <c r="D68" t="s">
-        <v>326</v>
-      </c>
-      <c r="E68" s="12" t="str">
-        <f>CONCATENATE(Table1[[#This Row],[Jugador1]]," - ",Table1[[#This Row],[Jugador2]])</f>
-        <v>Nicanor Hermosilla - J. Antonio Berdonces</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
         <v>0</v>
       </c>
     </row>
@@ -3399,263 +3358,263 @@
   <sheetData>
     <row r="1" spans="1:3" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B5" s="5">
         <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="5">
         <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5">
         <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B13" s="6">
         <v>3875</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B14" s="6">
         <v>3875</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B15" s="5">
         <v>58</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B16" s="5">
         <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B20" s="6">
         <v>80625</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B21" s="5">
         <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B22" s="5">
         <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B23" s="6">
         <v>19375</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B24" s="6">
         <v>39875</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B25">
         <v>38.25</v>
@@ -3663,7 +3622,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B26">
         <v>58.5</v>
@@ -3671,7 +3630,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27">
         <v>68.75</v>
@@ -3679,7 +3638,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28">
         <v>6.125</v>
@@ -3687,7 +3646,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29">
         <v>32</v>
@@ -3695,7 +3654,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B30">
         <v>34.5</v>
@@ -3703,7 +3662,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B31" s="8">
         <v>40.875</v>
@@ -3711,7 +3670,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B32">
         <v>19.5</v>
@@ -3719,7 +3678,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B33">
         <v>40.75</v>
@@ -3727,7 +3686,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34">
         <v>82.25</v>
@@ -3735,7 +3694,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>53</v>
@@ -3743,7 +3702,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B36">
         <v>53</v>
@@ -3751,7 +3710,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37">
         <v>67.5</v>
@@ -3759,7 +3718,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38">
         <v>67.5</v>

--- a/sources/02032026/Liga2026-ParejasIniciales-Provisional.xlsx
+++ b/sources/02032026/Liga2026-ParejasIniciales-Provisional.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hermosil\Documents\github\club-padel-ui\sources\02032026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3DF5E0A-7C87-4C31-BC91-396887320673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F27049-F3BC-497D-9748-2E3185C746AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31920" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parejas" sheetId="1" r:id="rId1"/>
-    <sheet name="Retirados" sheetId="2" r:id="rId2"/>
+    <sheet name="ListadoPreLiga" sheetId="1" r:id="rId1"/>
+    <sheet name="Parejas" sheetId="2" r:id="rId2"/>
+    <sheet name="Retirados" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_7CA3FEC5_A438_4C76_BE95_94AF2C9DD9DC_.wvu.FilterData" localSheetId="0" hidden="1">Parejas!$A$1:$E$71</definedName>
+    <definedName name="Z_455FAC2B_6350_4C42_98AE_AB0163447A05_.wvu.FilterData" localSheetId="1" hidden="1">Parejas!$A$1:$E$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
-    <customWorkbookView name="Table1 filter view" guid="{7CA3FEC5-A438-4C76-BE95-94AF2C9DD9DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Table1 filter view" guid="{455FAC2B-6350-4C42-98AE-AB0163447A05}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,14 +37,242 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="SJQwUbectnw47vJrdWCl5jtGrerucFZda6JJk4knx8U="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="9tZz1K8DanMZYh4+m7sKFCzcHdyrvRV+c1EMgd80eF0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="277">
+  <si>
+    <t>Listado y Posiciones Liga Febrero - Marzo 2026</t>
+  </si>
+  <si>
+    <t>Posición</t>
+  </si>
+  <si>
+    <t>División</t>
+  </si>
+  <si>
+    <t>Parejas</t>
+  </si>
+  <si>
+    <t>Grego - Luis Ángel</t>
+  </si>
+  <si>
+    <t>Happy - Pedro Correas</t>
+  </si>
+  <si>
+    <t>Junior - Alfonsito</t>
+  </si>
+  <si>
+    <t>Santi Molina - Gusi</t>
+  </si>
+  <si>
+    <t>Manolo Gómez - Joaquín Gea</t>
+  </si>
+  <si>
+    <t>Jose Ramón - Ramón Piedra</t>
+  </si>
+  <si>
+    <t>Fabián Morata - Raúl Olivetti</t>
+  </si>
+  <si>
+    <t>Loren Portillo - Juanmi Sanabria</t>
+  </si>
+  <si>
+    <t>Albertillo - Marcos Moreno</t>
+  </si>
+  <si>
+    <t>Manuel Choto - Julián</t>
+  </si>
+  <si>
+    <t>Álvaro Molina - Jesús Rodrigo</t>
+  </si>
+  <si>
+    <t>Javi Castillo - Sergio Campoy</t>
+  </si>
+  <si>
+    <t>Pollo - Chema</t>
+  </si>
+  <si>
+    <t>David Bellido - Manuel Bellido</t>
+  </si>
+  <si>
+    <t>Curro - Julio Carabias</t>
+  </si>
+  <si>
+    <t>Pablo Cano - Víctor Ocaña</t>
+  </si>
+  <si>
+    <t>Cazorla - Manolillo</t>
+  </si>
+  <si>
+    <t>Fran Collado - Mariano</t>
+  </si>
+  <si>
+    <t>Juanjo - Juan Carlos Illescas</t>
+  </si>
+  <si>
+    <t>Vivi - Juan Sánchez Sr.</t>
+  </si>
+  <si>
+    <t>Raúl Garcia - Alvarito</t>
+  </si>
+  <si>
+    <t>Adrian Camacho - David Hermosilla</t>
+  </si>
+  <si>
+    <t>Sebastián Pancorbo - Rafael Cordones</t>
+  </si>
+  <si>
+    <t>Luis Mena - Carlos Domínguez</t>
+  </si>
+  <si>
+    <t>Juanele - Javi Granados</t>
+  </si>
+  <si>
+    <t>Loren Perea - Manuel Ortega</t>
+  </si>
+  <si>
+    <t>Salvita Jiménez - Sergio Garrote</t>
+  </si>
+  <si>
+    <t>Pepe Conde - Ángel Torres</t>
+  </si>
+  <si>
+    <t>Adrián Martínez - Jose David</t>
+  </si>
+  <si>
+    <t>Jose Alberto Navarro - Paco Rama</t>
+  </si>
+  <si>
+    <t>Adri Pérez Ibáñez - Antonio Girón</t>
+  </si>
+  <si>
+    <t>Juanji - Pedro Utrera</t>
+  </si>
+  <si>
+    <t>Manuel Vilchez - Daniel Armenteros</t>
+  </si>
+  <si>
+    <t>Manu Morata - Joel Aguilera</t>
+  </si>
+  <si>
+    <t>Pedrito Almansa - Jose Alberto Agenjo</t>
+  </si>
+  <si>
+    <t>Antonio Ballesteros - Luismi</t>
+  </si>
+  <si>
+    <t>Jose Galvez - Alberto López</t>
+  </si>
+  <si>
+    <t>Rafael Castro - Francisco Reca</t>
+  </si>
+  <si>
+    <t>Ramón Ruiz - Gabriel Gálvez</t>
+  </si>
+  <si>
+    <t>Alejandro Ferro - Juan Ferro</t>
+  </si>
+  <si>
+    <t>Alberto Lomas - Juan Carlos Mesa</t>
+  </si>
+  <si>
+    <t>Antonio Jesús Martos - Fran Otto</t>
+  </si>
+  <si>
+    <t>Manuel Puri - Antonio Lara</t>
+  </si>
+  <si>
+    <t>Vanesa Platero - Luis Mena</t>
+  </si>
+  <si>
+    <t>José Manuel Jurado - Ángel Jurado</t>
+  </si>
+  <si>
+    <t>Javier Morón - Manuel Ruiz</t>
+  </si>
+  <si>
+    <t>Anselmo Martínez - Javi Porras</t>
+  </si>
+  <si>
+    <t>José Antonio Sequera - Antonio Luis Peña</t>
+  </si>
+  <si>
+    <t>Pablo Ruiz - Juan Manuel Lloris</t>
+  </si>
+  <si>
+    <t>Manolo Toribio - Raquel Fernández</t>
+  </si>
+  <si>
+    <t>Manuel Moreno - Álvaro López Garcia</t>
+  </si>
+  <si>
+    <t>Jesús Serra - Sergio Serra</t>
+  </si>
+  <si>
+    <t>Ruano - Cristina</t>
+  </si>
+  <si>
+    <t>Jose Manuel Ibañez - Ángel Villar</t>
+  </si>
+  <si>
+    <t>Ángel Chinchilla - Javier Escribano</t>
+  </si>
+  <si>
+    <t>Alberto Serrano - Jaime Baltanas</t>
+  </si>
+  <si>
+    <t>Sergio Campoy - Isa Monsalve</t>
+  </si>
+  <si>
+    <t>Manu Morata - Maria del Mar Morata</t>
+  </si>
+  <si>
+    <t>Emilio Briones Jr - Emilio Briones</t>
+  </si>
+  <si>
+    <t>Jose Carlos Jiménez - Alejandro Jiménez</t>
+  </si>
+  <si>
+    <t>Carlos Lozano - Alejandro Rueda</t>
+  </si>
+  <si>
+    <t>Vanessa Platero - Rocío Muñoz</t>
+  </si>
+  <si>
+    <t>Álvaro Cazorla - Rosa López</t>
+  </si>
+  <si>
+    <t>Tomas - Juan Carlos Romero</t>
+  </si>
+  <si>
+    <t>Miguel Cáliz - Ricardo García</t>
+  </si>
+  <si>
+    <t>Jose Alberto Navarro - Sandra Rodríguez</t>
+  </si>
+  <si>
+    <t>Laura - Mari Angeles</t>
+  </si>
+  <si>
+    <t>Miguel Angel Arenas - Rafa Robles</t>
+  </si>
+  <si>
+    <t>Santi Molina - Estefanía</t>
+  </si>
+  <si>
+    <t>Mari Ángeles - Laura</t>
+  </si>
+  <si>
+    <t>Jose Torres - Josemi</t>
+  </si>
+  <si>
+    <t>Oscar Donaire - Fran Delgado</t>
+  </si>
   <si>
     <t>OrdenInicial</t>
   </si>
@@ -75,61 +304,46 @@
     <t>Luis Ángel</t>
   </si>
   <si>
-    <t>Grego - Luis Ángel</t>
-  </si>
-  <si>
     <t>Happy</t>
   </si>
   <si>
     <t>Pedro Correas</t>
   </si>
   <si>
-    <t>Happy - Pedro Correas</t>
-  </si>
-  <si>
     <t>Junior</t>
   </si>
   <si>
     <t>Alfonsito</t>
   </si>
   <si>
-    <t>Junior - Alfonsito</t>
-  </si>
-  <si>
     <t>Santi Molina</t>
   </si>
   <si>
     <t>Gusi</t>
   </si>
   <si>
-    <t>Santi Molina - Gusi</t>
-  </si>
-  <si>
     <t>Manolo Gómez</t>
   </si>
   <si>
     <t>Joaquín Gea</t>
   </si>
   <si>
-    <t>Manolo Gómez - Joaquín Gea</t>
-  </si>
-  <si>
     <t>Jose Ramón</t>
   </si>
   <si>
     <t>Ramón Piedra</t>
   </si>
   <si>
-    <t>Jose Ramón - Ramón Piedra</t>
-  </si>
-  <si>
     <t>Fabián Morata</t>
   </si>
   <si>
     <t>Raúl Olivetti</t>
   </si>
   <si>
-    <t>Fabián Morata - Raúl Olivetti</t>
+    <t>Loren Portillo</t>
+  </si>
+  <si>
+    <t>Juanmi Sanabria</t>
   </si>
   <si>
     <t>Albertillo</t>
@@ -138,61 +352,46 @@
     <t>Marcos Moreno</t>
   </si>
   <si>
-    <t>Albertillo - Marcos Moreno</t>
-  </si>
-  <si>
     <t>Manuel Choto</t>
   </si>
   <si>
     <t>Julián</t>
   </si>
   <si>
-    <t>Manuel Choto - Julián</t>
-  </si>
-  <si>
     <t>Álvaro Molina</t>
   </si>
   <si>
     <t>Jesús Rodrigo</t>
   </si>
   <si>
-    <t>Álvaro Molina - Jesús Rodrigo</t>
-  </si>
-  <si>
     <t>Javi Castillo</t>
   </si>
   <si>
     <t>Sergio Campoy</t>
   </si>
   <si>
-    <t>Javi Castillo - Sergio Campoy</t>
-  </si>
-  <si>
     <t>Pollo</t>
   </si>
   <si>
     <t>Chema</t>
   </si>
   <si>
-    <t>Pollo - Chema</t>
-  </si>
-  <si>
-    <t>Loren Portillo</t>
-  </si>
-  <si>
-    <t>Juanmi Sanabria</t>
-  </si>
-  <si>
-    <t>Loren Portillo - Juanmi Sanabria</t>
-  </si>
-  <si>
     <t>David Bellido</t>
   </si>
   <si>
     <t>Manuel Bellido</t>
   </si>
   <si>
-    <t>David Bellido - Manuel Bellido</t>
+    <t>Curro</t>
+  </si>
+  <si>
+    <t>Julio Carabias</t>
+  </si>
+  <si>
+    <t>Cazorla</t>
+  </si>
+  <si>
+    <t>Manolillo</t>
   </si>
   <si>
     <t>Pablo Cano</t>
@@ -201,61 +400,40 @@
     <t>Víctor Ocaña</t>
   </si>
   <si>
-    <t>Pablo Cano - Víctor Ocaña</t>
-  </si>
-  <si>
-    <t>Manolillo</t>
-  </si>
-  <si>
-    <t>Matias</t>
-  </si>
-  <si>
-    <t>Manolillo - Matias</t>
-  </si>
-  <si>
     <t>Fran Collado</t>
   </si>
   <si>
     <t>Mariano</t>
   </si>
   <si>
-    <t>Fran Collado - Mariano</t>
-  </si>
-  <si>
     <t>Juanjo</t>
   </si>
   <si>
     <t>Juan Carlos Illescas</t>
   </si>
   <si>
-    <t>Juanjo - Juan Carlos Illescas</t>
-  </si>
-  <si>
     <t>Vivi</t>
   </si>
   <si>
     <t>Juan Sánchez Sr.</t>
   </si>
   <si>
-    <t>Vivi - Juan Sánchez Sr.</t>
-  </si>
-  <si>
     <t>Raúl Garcia</t>
   </si>
   <si>
     <t>Alvarito</t>
   </si>
   <si>
-    <t>Raúl Garcia - Alvarito</t>
-  </si>
-  <si>
     <t>Adrian Camacho</t>
   </si>
   <si>
     <t>David Hermosilla</t>
   </si>
   <si>
-    <t>Adrian Camacho - David Hermosilla</t>
+    <t>Sebastián Pancorbo</t>
+  </si>
+  <si>
+    <t>Rafael Cordones</t>
   </si>
   <si>
     <t>Luis Mena</t>
@@ -264,249 +442,165 @@
     <t>Carlos Domínguez</t>
   </si>
   <si>
-    <t>Luis Mena - Carlos Domínguez</t>
-  </si>
-  <si>
     <t>Juanele</t>
   </si>
   <si>
     <t>Javi Granados</t>
   </si>
   <si>
-    <t>Juanele - Javi Granados</t>
-  </si>
-  <si>
-    <t>Curro</t>
-  </si>
-  <si>
-    <t>Julio Carabias</t>
-  </si>
-  <si>
-    <t>Curro - Julio Carabias</t>
-  </si>
-  <si>
     <t>Loren Perea</t>
   </si>
   <si>
     <t>Manuel Ortega</t>
   </si>
   <si>
-    <t>Loren Perea - Manuel Ortega</t>
-  </si>
-  <si>
     <t>Salvita Jiménez</t>
   </si>
   <si>
     <t>Sergio Garrote</t>
   </si>
   <si>
-    <t>Salvita Jiménez - Sergio Garrote</t>
-  </si>
-  <si>
     <t>Pepe Conde</t>
   </si>
   <si>
     <t>Ángel Torres</t>
   </si>
   <si>
-    <t>Pepe Conde - Ángel Torres</t>
-  </si>
-  <si>
     <t>Adrián Martínez</t>
   </si>
   <si>
     <t>Jose David</t>
   </si>
   <si>
-    <t>Adrián Martínez - Jose David</t>
-  </si>
-  <si>
     <t>Jose Alberto Navarro</t>
   </si>
   <si>
     <t>Paco Rama</t>
   </si>
   <si>
-    <t>Jose Alberto Navarro - Paco Rama</t>
-  </si>
-  <si>
     <t>Adri Pérez Ibáñez</t>
   </si>
   <si>
     <t>Antonio Girón</t>
   </si>
   <si>
-    <t>Adri Pérez Ibáñez - Antonio Girón</t>
-  </si>
-  <si>
     <t>Juanji</t>
   </si>
   <si>
     <t>Pedro Utrera</t>
   </si>
   <si>
-    <t>Juanji - Pedro Utrera</t>
-  </si>
-  <si>
     <t>Manuel Vilchez</t>
   </si>
   <si>
     <t>Daniel Armenteros</t>
   </si>
   <si>
-    <t>Manuel Vilchez - Daniel Armenteros</t>
-  </si>
-  <si>
     <t>Manu Morata</t>
   </si>
   <si>
     <t>Joel Aguilera</t>
   </si>
   <si>
-    <t>Manu Morata - Joel Aguilera</t>
-  </si>
-  <si>
     <t>Pedrito Almansa</t>
   </si>
   <si>
     <t>Jose Alberto Agenjo</t>
   </si>
   <si>
-    <t>Pedrito Almansa - Jose Alberto Agenjo</t>
-  </si>
-  <si>
     <t>Antonio Ballesteros</t>
   </si>
   <si>
     <t>Luismi</t>
   </si>
   <si>
-    <t>Antonio Ballesteros - Luismi</t>
-  </si>
-  <si>
     <t>Jose Galvez</t>
   </si>
   <si>
     <t>Alberto López</t>
   </si>
   <si>
-    <t>Jose Galvez - Alberto López</t>
-  </si>
-  <si>
     <t>Rafael Castro</t>
   </si>
   <si>
     <t>Francisco Reca</t>
   </si>
   <si>
-    <t>Rafael Castro - Francisco Reca</t>
-  </si>
-  <si>
     <t>Ramón Ruiz</t>
   </si>
   <si>
     <t>Gabriel Gálvez</t>
   </si>
   <si>
-    <t>Ramón Ruiz - Gabriel Gálvez</t>
-  </si>
-  <si>
     <t>Alejandro Ferro</t>
   </si>
   <si>
     <t>Juan Ferro</t>
   </si>
   <si>
-    <t>Alejandro Ferro - Juan Ferro</t>
-  </si>
-  <si>
     <t>Alberto Lomas</t>
   </si>
   <si>
     <t>Juan Carlos Mesa</t>
   </si>
   <si>
-    <t>Alberto Lomas - Juan Carlos Mesa</t>
+    <t>Manuel Puri</t>
+  </si>
+  <si>
+    <t>Antonio Lara</t>
   </si>
   <si>
     <t>Vanesa Platero</t>
   </si>
   <si>
-    <t>Vanesa Platero - Luis Mena</t>
-  </si>
-  <si>
     <t>José Manuel Jurado</t>
   </si>
   <si>
     <t>Ángel Jurado</t>
   </si>
   <si>
-    <t>José Manuel Jurado - Ángel Jurado</t>
-  </si>
-  <si>
     <t>Javier Morón</t>
   </si>
   <si>
     <t>Manuel Ruiz</t>
   </si>
   <si>
-    <t>Javier Morón - Manuel Ruiz</t>
-  </si>
-  <si>
     <t>Anselmo Martínez</t>
   </si>
   <si>
     <t>Javi Porras</t>
   </si>
   <si>
-    <t>Anselmo Martínez - Javi Porras</t>
-  </si>
-  <si>
     <t>José Antonio Sequera</t>
   </si>
   <si>
     <t>Antonio Luis Peña</t>
   </si>
   <si>
-    <t>José Antonio Sequera - Antonio Luis Peña</t>
-  </si>
-  <si>
     <t>Pablo Ruiz</t>
   </si>
   <si>
     <t>Juan Manuel Lloris</t>
   </si>
   <si>
-    <t>Pablo Ruiz - Juan Manuel Lloris</t>
-  </si>
-  <si>
     <t>Manolo Toribio</t>
   </si>
   <si>
     <t>Raquel Fernández</t>
   </si>
   <si>
-    <t>Manolo Toribio - Raquel Fernández</t>
-  </si>
-  <si>
     <t>Manuel Moreno</t>
   </si>
   <si>
     <t>Álvaro López Garcia</t>
   </si>
   <si>
-    <t>Manuel Moreno - Álvaro López Garcia</t>
-  </si>
-  <si>
     <t>Emilio Briones Jr</t>
   </si>
   <si>
     <t>Emilio Briones</t>
   </si>
   <si>
-    <t>Emilio Briones Jr - Emilio Briones</t>
-  </si>
-  <si>
     <t>Nicanor Hermosilla</t>
   </si>
   <si>
@@ -525,75 +619,48 @@
     <t>Sergio Serra</t>
   </si>
   <si>
-    <t>Jesús Serra - Sergio Serra</t>
-  </si>
-  <si>
     <t>Ruano</t>
   </si>
   <si>
     <t>Cristina</t>
   </si>
   <si>
-    <t>Ruano - Cristina</t>
-  </si>
-  <si>
     <t>Jose Manuel Ibañez</t>
   </si>
   <si>
     <t>Ángel Villar</t>
   </si>
   <si>
-    <t>Jose Manuel Ibañez - Ángel Villar</t>
-  </si>
-  <si>
     <t>Ángel Chinchilla</t>
   </si>
   <si>
     <t>Javier Escribano</t>
   </si>
   <si>
-    <t>Ángel Chinchilla - Javier Escribano</t>
-  </si>
-  <si>
     <t>Alberto Serrano</t>
   </si>
   <si>
     <t>Jaime Baltanas</t>
   </si>
   <si>
-    <t>Alberto Serrano - Jaime Baltanas</t>
-  </si>
-  <si>
     <t>Isa Monsalve</t>
   </si>
   <si>
-    <t>Sergio Campoy - Isa Monsalve</t>
-  </si>
-  <si>
     <t>Maria del Mar Morata</t>
   </si>
   <si>
-    <t>Manu Morata - Maria del Mar Morata</t>
-  </si>
-  <si>
     <t>Jose Carlos Jiménez</t>
   </si>
   <si>
     <t>Alejandro Jiménez</t>
   </si>
   <si>
-    <t>Jose Carlos Jiménez - Alejandro Jiménez</t>
-  </si>
-  <si>
     <t>Carlos Lozano</t>
   </si>
   <si>
     <t>Alejandro Rueda</t>
   </si>
   <si>
-    <t>Carlos Lozano - Alejandro Rueda</t>
-  </si>
-  <si>
     <t>Miguel Marmol</t>
   </si>
   <si>
@@ -606,69 +673,60 @@
     <t>Rocío Muñoz</t>
   </si>
   <si>
-    <t>Vanessa Platero - Rocío Muñoz</t>
-  </si>
-  <si>
     <t>Álvaro Cazorla</t>
   </si>
   <si>
     <t>Rosa López</t>
   </si>
   <si>
-    <t>Álvaro Cazorla - Rosa López</t>
+    <t>Tomas</t>
+  </si>
+  <si>
+    <t>Juan Carlos Romero</t>
+  </si>
+  <si>
+    <t>Miguel Cáliz</t>
+  </si>
+  <si>
+    <t>Ricardo García</t>
   </si>
   <si>
     <t>Sandra Rodríguez</t>
   </si>
   <si>
-    <t>Jose Alberto Navarro - Sandra Rodríguez</t>
-  </si>
-  <si>
-    <t>Rosa López - Isa Monsalve</t>
-  </si>
-  <si>
     <t>Antonio Jesús Martos</t>
   </si>
   <si>
     <t>Fran Otto</t>
   </si>
   <si>
-    <t>Antonio Jesús Martos - Fran Otto</t>
-  </si>
-  <si>
     <t>Laura</t>
   </si>
   <si>
     <t>Mari Angeles</t>
   </si>
   <si>
-    <t>Laura - Mari Angeles</t>
-  </si>
-  <si>
     <t>Miguel Angel Arenas</t>
   </si>
   <si>
     <t>Rafa Robles</t>
   </si>
   <si>
-    <t>Miguel Angel Arenas - Rafa Robles</t>
-  </si>
-  <si>
-    <t>Agenjo</t>
-  </si>
-  <si>
     <t>Estefanía</t>
   </si>
   <si>
-    <t>Agenjo - Estefanía</t>
-  </si>
-  <si>
     <t>Almudena</t>
   </si>
   <si>
     <t>Inma Villacañas</t>
   </si>
   <si>
+    <t>Manuel Juarez</t>
+  </si>
+  <si>
+    <t>Antonio García</t>
+  </si>
+  <si>
     <t>Quitados Superliga</t>
   </si>
   <si>
@@ -798,9 +856,6 @@
     <t>David Ballesteros</t>
   </si>
   <si>
-    <t>Ricardo García</t>
-  </si>
-  <si>
     <t>Manuel Garzón</t>
   </si>
   <si>
@@ -817,13 +872,28 @@
   </si>
   <si>
     <t>Manuel Cerezo</t>
+  </si>
+  <si>
+    <t>X -Y</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="17"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,12 +911,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -874,12 +938,36 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9DAF8"/>
+        <bgColor rgb="FFC9DAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A86E8"/>
+        <bgColor rgb="FF4A86E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1027,70 +1115,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1179,23 +1278,43 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
-  <tableStyles count="4">
-    <tableStyle name="Parejas-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+  <tableStyles count="5">
+    <tableStyle name="ListadoPreLiga-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="secondRowStripe" dxfId="10"/>
+    </tableStyle>
+    <tableStyle name="Parejas-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" size="0" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Parejas-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Parejas-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="firstRowStripe" dxfId="5"/>
       <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
-    <tableStyle name="Parejas-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+    <tableStyle name="Parejas-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
       <tableStyleElement type="firstRowStripe" dxfId="3"/>
       <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
-    <tableStyle name="Parejas-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+    <tableStyle name="Parejas-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
@@ -1212,38 +1331,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:E71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A4:C82" headerRowCount="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3"/>
+  </tableColumns>
+  <tableStyleInfo name="ListadoPreLiga-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="A1:E76">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="OrdenInicial"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Division"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Jugador1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Jugador2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Pareja"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="OrdenInicial"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Division"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Jugador1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Jugador2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Pareja"/>
   </tableColumns>
   <tableStyleInfo name="Parejas-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_1" displayName="Table_1" ref="J32:R34" headerRowCount="0">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_2" displayName="Table_2" ref="J33:R35" headerRowCount="0">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Column5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Column6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Column7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Column8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Column9"/>
-  </tableColumns>
-  <tableStyleInfo name="Parejas-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_2" displayName="Table_2" ref="K53:R54" headerRowCount="0">
-  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Column2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Column3"/>
@@ -1252,19 +1365,36 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Column6"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Column7"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Column8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Column9"/>
+  </tableColumns>
+  <tableStyleInfo name="Parejas-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table_3" displayName="Table_3" ref="K55:R56" headerRowCount="0">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Column4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Column5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Column6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Column7"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Column8"/>
   </tableColumns>
   <tableStyleInfo name="Parejas-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table_3" displayName="Table_3" ref="H70:L70" headerRowCount="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table_4" displayName="Table_4" ref="H73:L73" headerRowCount="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Column5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Column4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="Parejas-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1468,7 +1598,917 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1002"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C82"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="36.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2">
+        <v>4</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2">
+        <v>4</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2">
+        <v>4</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2">
+        <v>4</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2">
+        <v>4</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2">
+        <v>4</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2">
+        <v>4</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>35</v>
+      </c>
+      <c r="B38" s="2">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>36</v>
+      </c>
+      <c r="B39" s="2">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>37</v>
+      </c>
+      <c r="B40" s="2">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>38</v>
+      </c>
+      <c r="B41" s="2">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>39</v>
+      </c>
+      <c r="B42" s="2">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>40</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>41</v>
+      </c>
+      <c r="B44" s="2">
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>44</v>
+      </c>
+      <c r="B47" s="2">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>45</v>
+      </c>
+      <c r="B48" s="2">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>46</v>
+      </c>
+      <c r="B49" s="2">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>47</v>
+      </c>
+      <c r="B50" s="2">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>48</v>
+      </c>
+      <c r="B51" s="2">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>49</v>
+      </c>
+      <c r="B52" s="2">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>51</v>
+      </c>
+      <c r="B54" s="2">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>52</v>
+      </c>
+      <c r="B55" s="2">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>53</v>
+      </c>
+      <c r="B56" s="2">
+        <v>7</v>
+      </c>
+      <c r="C56" s="3" t="str">
+        <f>CONCATENATE(Parejas!$C54," - ",Parejas!$D54)</f>
+        <v>David Camara - Adrian Sáez</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>54</v>
+      </c>
+      <c r="B57" s="2">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>55</v>
+      </c>
+      <c r="B58" s="2">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>56</v>
+      </c>
+      <c r="B59" s="2">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>57</v>
+      </c>
+      <c r="B60" s="2">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>58</v>
+      </c>
+      <c r="B61" s="2">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>59</v>
+      </c>
+      <c r="B62" s="2">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>60</v>
+      </c>
+      <c r="B63" s="2">
+        <v>7</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>61</v>
+      </c>
+      <c r="B64" s="2">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>62</v>
+      </c>
+      <c r="B65" s="2">
+        <v>8</v>
+      </c>
+      <c r="C65" s="2" t="str">
+        <f>CONCATENATE(Parejas!$C53," - ",Parejas!$D53)</f>
+        <v>Nicanor Hermosilla - J. Antonio Berdonces</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>63</v>
+      </c>
+      <c r="B66" s="2">
+        <v>8</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>64</v>
+      </c>
+      <c r="B67" s="2">
+        <v>8</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>65</v>
+      </c>
+      <c r="B68" s="2">
+        <v>8</v>
+      </c>
+      <c r="C68" s="2" t="str">
+        <f>CONCATENATE(Parejas!$C64," - ",Parejas!$D64)</f>
+        <v>Miguel Marmol - Fernando Cubero</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>66</v>
+      </c>
+      <c r="B69" s="2">
+        <v>8</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>67</v>
+      </c>
+      <c r="B70" s="2">
+        <v>8</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>68</v>
+      </c>
+      <c r="B71" s="2">
+        <v>8</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>69</v>
+      </c>
+      <c r="B72" s="2">
+        <v>8</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>70</v>
+      </c>
+      <c r="B73" s="2">
+        <v>9</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>71</v>
+      </c>
+      <c r="B74" s="2">
+        <v>9</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>72</v>
+      </c>
+      <c r="B75" s="2">
+        <v>9</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>73</v>
+      </c>
+      <c r="B76" s="2">
+        <v>9</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>74</v>
+      </c>
+      <c r="B77" s="2">
+        <v>9</v>
+      </c>
+      <c r="C77" s="2" t="str">
+        <f>CONCATENATE(Parejas!$C74," - ",Parejas!$D74)</f>
+        <v>Almudena - Inma Villacañas</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>75</v>
+      </c>
+      <c r="B78" s="2">
+        <v>9</v>
+      </c>
+      <c r="C78" s="2" t="str">
+        <f>CONCATENATE(Parejas!$C75," - ",Parejas!$D75)</f>
+        <v>Manuel Juarez - Antonio García</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>76</v>
+      </c>
+      <c r="B79" s="2">
+        <v>9</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>77</v>
+      </c>
+      <c r="B80" s="2">
+        <v>9</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>78</v>
+      </c>
+      <c r="B81" s="2">
+        <v>9</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:R1005"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
@@ -1480,1858 +2520,1966 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="13">
+        <v>78.25</v>
+      </c>
+      <c r="G2" s="13">
+        <v>78.25</v>
+      </c>
+      <c r="H2" s="14">
+        <v>156.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="13">
+        <v>89.75</v>
+      </c>
+      <c r="G3" s="13">
+        <v>83.5</v>
+      </c>
+      <c r="H3" s="14">
+        <v>173.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="16">
+        <v>125</v>
+      </c>
+      <c r="G4" s="16">
+        <v>125</v>
+      </c>
+      <c r="H4" s="17">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="13">
+        <v>85.25</v>
+      </c>
+      <c r="G5" s="13">
+        <v>72.25</v>
+      </c>
+      <c r="H5" s="14">
+        <v>157.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="13">
+        <v>91.75</v>
+      </c>
+      <c r="G6" s="13">
+        <v>91.75</v>
+      </c>
+      <c r="H6" s="14">
+        <v>183.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="16">
+        <v>101625</v>
+      </c>
+      <c r="G7" s="16">
+        <v>66625</v>
+      </c>
+      <c r="H7" s="14">
+        <v>168.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="16">
+        <v>83625</v>
+      </c>
+      <c r="G8" s="16">
+        <v>83125</v>
+      </c>
+      <c r="H8" s="14">
+        <v>166.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11">
+        <v>1</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="13">
+        <v>92.25</v>
+      </c>
+      <c r="G9" s="16">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H9" s="14">
+        <v>92.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C10" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="16">
+        <v>76895</v>
+      </c>
+      <c r="G10" s="16">
+        <v>50375</v>
+      </c>
+      <c r="H10" s="14">
+        <v>127.27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="16">
+        <v>68</v>
+      </c>
+      <c r="G11" s="16">
+        <v>68</v>
+      </c>
+      <c r="H11" s="17">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11">
+        <v>2</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="13">
+        <v>87.75</v>
+      </c>
+      <c r="G12" s="16">
+        <v>95375</v>
+      </c>
+      <c r="H12" s="17">
+        <v>183125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11">
+        <v>2</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="13">
+        <v>93.25</v>
+      </c>
+      <c r="G13" s="16">
+        <v>69</v>
+      </c>
+      <c r="H13" s="14">
+        <v>162.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11">
+        <v>2</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11">
+        <v>2</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11">
+        <v>2</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="16">
+        <v>74</v>
+      </c>
+      <c r="G16" s="13">
+        <v>53.75</v>
+      </c>
+      <c r="H16" s="14">
+        <v>127.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11">
+        <v>2</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C18" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="16">
+        <v>59375</v>
+      </c>
+      <c r="G18" s="16">
+        <v>34375</v>
+      </c>
+      <c r="H18" s="14">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11">
+        <v>3</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="13">
+        <v>70.5</v>
+      </c>
+      <c r="G19" s="13">
+        <v>70.5</v>
+      </c>
+      <c r="H19" s="17">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11">
+        <v>3</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="16">
+        <v>62</v>
+      </c>
+      <c r="G20" s="13">
+        <v>33.25</v>
+      </c>
+      <c r="H20" s="14">
+        <v>95.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11">
+        <v>3</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="16">
+        <v>68</v>
+      </c>
+      <c r="G21" s="13">
+        <v>30.25</v>
+      </c>
+      <c r="H21" s="14">
+        <v>98.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11">
+        <v>3</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="16">
+        <v>18</v>
+      </c>
+      <c r="G22" s="16">
+        <v>58</v>
+      </c>
+      <c r="H22" s="17">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11">
+        <v>3</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="16">
+        <v>0</v>
+      </c>
+      <c r="G23" s="16">
+        <v>66625</v>
+      </c>
+      <c r="H23" s="17">
+        <v>66625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11">
+        <v>3</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="11">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11">
+        <v>3</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="16">
+        <v>68</v>
+      </c>
+      <c r="G25" s="16">
+        <v>72375</v>
+      </c>
+      <c r="H25" s="17">
+        <v>140375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11">
+        <v>3</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="13">
+        <v>59.5</v>
+      </c>
+      <c r="G26" s="16">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="C27" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="16">
+        <v>55</v>
+      </c>
+      <c r="G27" s="13">
+        <v>59.5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>114.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11">
+        <v>4</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="13">
+        <v>45.25</v>
+      </c>
+      <c r="G28" s="13">
+        <v>28.25</v>
+      </c>
+      <c r="H28" s="14">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11">
+        <v>4</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="13">
+        <v>42.75</v>
+      </c>
+      <c r="G29" s="13">
+        <v>20.75</v>
+      </c>
+      <c r="H29" s="14">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11">
+        <v>4</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="16">
+        <v>53125</v>
+      </c>
+      <c r="G30" s="16">
+        <v>23625</v>
+      </c>
+      <c r="H30" s="14">
+        <v>76.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11">
+        <v>4</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="13">
+        <v>43.5</v>
+      </c>
+      <c r="G31" s="13">
+        <v>43.5</v>
+      </c>
+      <c r="H31" s="17">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>31</v>
+      </c>
+      <c r="B32" s="11">
+        <v>4</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="13">
+        <v>56.25</v>
+      </c>
+      <c r="G32" s="13">
+        <v>17.75</v>
+      </c>
+      <c r="H32" s="17">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11">
+        <v>4</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="16">
+        <v>45875</v>
+      </c>
+      <c r="G33" s="16">
+        <v>23875</v>
+      </c>
+      <c r="H33" s="14">
+        <v>69.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11">
+        <v>4</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="C35" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="16">
+        <v>41125</v>
+      </c>
+      <c r="G35" s="16">
+        <v>17625</v>
+      </c>
+      <c r="H35" s="14">
+        <v>58.75</v>
+      </c>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+    </row>
+    <row r="36" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>35</v>
+      </c>
+      <c r="B36" s="11">
+        <v>5</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="13">
+        <v>57.75</v>
+      </c>
+      <c r="G36" s="13">
+        <v>22.75</v>
+      </c>
+      <c r="H36" s="14">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>36</v>
+      </c>
+      <c r="B37" s="11">
+        <v>5</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="13">
+        <v>39.75</v>
+      </c>
+      <c r="G37" s="13">
+        <v>39.75</v>
+      </c>
+      <c r="H37" s="14">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11">
+        <v>5</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="13">
+        <v>35.25</v>
+      </c>
+      <c r="G38" s="13">
+        <v>15.5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11">
+        <v>5</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="16">
+        <v>30125</v>
+      </c>
+      <c r="G39" s="16">
+        <v>30125</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11">
+        <v>5</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="16">
+        <v>42875</v>
+      </c>
+      <c r="G40" s="16">
+        <v>31875</v>
+      </c>
+      <c r="H40" s="14">
+        <v>74.75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>40</v>
+      </c>
+      <c r="B41" s="11">
+        <v>5</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="16">
+        <v>29875</v>
+      </c>
+      <c r="G41" s="16">
+        <v>29875</v>
+      </c>
+      <c r="H41" s="14">
+        <v>59.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11">
+        <v>5</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="16">
+        <v>34125</v>
+      </c>
+      <c r="G42" s="16">
+        <v>18125</v>
+      </c>
+      <c r="H42" s="14">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="11">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11">
+        <v>5</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="14"/>
+    </row>
+    <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="C44" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F44" s="16">
+        <v>28375</v>
+      </c>
+      <c r="G44" s="16">
+        <v>28375</v>
+      </c>
+      <c r="H44" s="14">
+        <v>56.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11">
+        <v>6</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" s="13">
+        <v>25.75</v>
+      </c>
+      <c r="G45" s="13">
+        <v>25.75</v>
+      </c>
+      <c r="H45" s="14">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11">
+        <v>6</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="13">
+        <v>28.25</v>
+      </c>
+      <c r="G46" s="13">
+        <v>28.25</v>
+      </c>
+      <c r="H46" s="14">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>46</v>
+      </c>
+      <c r="B47" s="11">
+        <v>6</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F47" s="13">
+        <v>18.5</v>
+      </c>
+      <c r="G47" s="13">
+        <v>18.5</v>
+      </c>
+      <c r="H47" s="17">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>47</v>
+      </c>
+      <c r="B48" s="11">
+        <v>6</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="16">
+        <v>26125</v>
+      </c>
+      <c r="G48" s="16">
+        <v>26125</v>
+      </c>
+      <c r="H48" s="14">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11">
+        <v>6</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" s="13">
+        <v>15.25</v>
+      </c>
+      <c r="G49" s="13">
+        <v>15.25</v>
+      </c>
+      <c r="H49" s="14">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>49</v>
+      </c>
+      <c r="B50" s="11">
+        <v>6</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" s="16">
+        <v>24625</v>
+      </c>
+      <c r="G50" s="16">
+        <v>24625</v>
+      </c>
+      <c r="H50" s="14">
+        <v>49.25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="11">
+        <v>50</v>
+      </c>
+      <c r="B51" s="11">
+        <v>6</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="16">
+        <v>29</v>
+      </c>
+      <c r="G51" s="16">
+        <v>6125</v>
+      </c>
+      <c r="H51" s="17">
+        <v>35125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="11">
+        <v>51</v>
+      </c>
+      <c r="B52" s="11">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="C52" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="16">
+        <v>0</v>
+      </c>
+      <c r="G52" s="16">
+        <v>20875</v>
+      </c>
+      <c r="H52" s="17">
+        <v>20875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="11">
+        <v>52</v>
+      </c>
+      <c r="B53" s="11">
+        <v>7</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53" s="18" t="str">
+        <f>CONCATENATE(Parejas!$C53," - ",Parejas!$D53)</f>
+        <v>Nicanor Hermosilla - J. Antonio Berdonces</v>
+      </c>
+      <c r="F53" s="16">
+        <v>0</v>
+      </c>
+      <c r="G53" s="16">
+        <v>0</v>
+      </c>
+      <c r="H53" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>53</v>
+      </c>
+      <c r="B54" s="11">
+        <v>7</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E54" s="20" t="str">
+        <f>CONCATENATE(Parejas!$C54," - ",Parejas!$D54)</f>
+        <v>David Camara - Adrian Sáez</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>54</v>
+      </c>
+      <c r="B55" s="11">
+        <v>7</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="13">
+        <v>17.25</v>
+      </c>
+      <c r="G55" s="13">
+        <v>5.75</v>
+      </c>
+      <c r="H55" s="17">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>55</v>
+      </c>
+      <c r="B56" s="11">
+        <v>7</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="13">
+        <v>22.5</v>
+      </c>
+      <c r="G56" s="16">
+        <v>9</v>
+      </c>
+      <c r="H56" s="14">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>56</v>
+      </c>
+      <c r="B57" s="11">
+        <v>7</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F57" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="G57" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="H57" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>57</v>
+      </c>
+      <c r="B58" s="11">
+        <v>7</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F58" s="13">
+        <v>12.75</v>
+      </c>
+      <c r="G58" s="13">
+        <v>5.25</v>
+      </c>
+      <c r="H58" s="17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>58</v>
+      </c>
+      <c r="B59" s="11">
+        <v>7</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="13">
+        <v>15.75</v>
+      </c>
+      <c r="G59" s="13">
+        <v>15.75</v>
+      </c>
+      <c r="H59" s="14">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>59</v>
+      </c>
+      <c r="B60" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C60" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F60" s="16">
+        <v>12125</v>
+      </c>
+      <c r="G60" s="16">
+        <v>12125</v>
+      </c>
+      <c r="H60" s="14">
+        <v>24.25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>60</v>
+      </c>
+      <c r="B61" s="11">
+        <v>8</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F61" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="G61" s="16">
+        <v>18125</v>
+      </c>
+      <c r="H61" s="17">
+        <v>25625</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>61</v>
+      </c>
+      <c r="B62" s="11">
+        <v>8</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F62" s="16">
+        <v>17125</v>
+      </c>
+      <c r="G62" s="16">
+        <v>17125</v>
+      </c>
+      <c r="H62" s="14">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>62</v>
+      </c>
+      <c r="B63" s="11">
+        <v>8</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F63" s="13">
+        <v>8.75</v>
+      </c>
+      <c r="G63" s="13">
+        <v>8.75</v>
+      </c>
+      <c r="H63" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>63</v>
+      </c>
+      <c r="B64" s="11">
+        <v>8</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E64" s="18" t="str">
+        <f>CONCATENATE(Parejas!$C64," - ",Parejas!$D64)</f>
+        <v>Miguel Marmol - Fernando Cubero</v>
+      </c>
+      <c r="F64" s="16">
+        <v>0</v>
+      </c>
+      <c r="G64" s="13">
+        <v>1.25</v>
+      </c>
+      <c r="H64" s="14">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="11">
+        <v>64</v>
+      </c>
+      <c r="B65" s="11">
+        <v>8</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F65" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="G65" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="H65" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="11">
+        <v>65</v>
+      </c>
+      <c r="B66" s="11">
+        <v>8</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F66" s="16">
+        <v>11</v>
+      </c>
+      <c r="G66" s="16">
+        <v>11</v>
+      </c>
+      <c r="H66" s="17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="11">
+        <v>66</v>
+      </c>
+      <c r="B67" s="11">
+        <v>8</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" s="16">
+        <v>0</v>
+      </c>
+      <c r="G67" s="16">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>67</v>
+      </c>
+      <c r="B68" s="11">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="7">
-        <v>78.25</v>
-      </c>
-      <c r="G2" s="7">
-        <v>78.25</v>
-      </c>
-      <c r="H2" s="8">
-        <v>156.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7">
-        <v>89.75</v>
-      </c>
-      <c r="G3" s="7">
-        <v>83.5</v>
-      </c>
-      <c r="H3" s="8">
-        <v>173.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="10">
-        <v>125</v>
-      </c>
-      <c r="G4" s="10">
-        <v>125</v>
-      </c>
-      <c r="H4" s="11">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="7">
-        <v>85.25</v>
-      </c>
-      <c r="G5" s="7">
-        <v>72.25</v>
-      </c>
-      <c r="H5" s="8">
-        <v>157.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="7">
-        <v>91.75</v>
-      </c>
-      <c r="G6" s="7">
-        <v>91.75</v>
-      </c>
-      <c r="H6" s="8">
-        <v>183.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="10">
-        <v>101625</v>
-      </c>
-      <c r="G7" s="10">
-        <v>66625</v>
-      </c>
-      <c r="H7" s="8">
-        <v>168.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="10">
-        <v>83625</v>
-      </c>
-      <c r="G8" s="10">
-        <v>83125</v>
-      </c>
-      <c r="H8" s="8">
-        <v>166.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="10">
-        <v>76895</v>
-      </c>
-      <c r="G9" s="10">
-        <v>50375</v>
-      </c>
-      <c r="H9" s="8">
-        <v>127.27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="C68" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="14"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="11">
+        <v>68</v>
+      </c>
+      <c r="B69" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
-        <v>2</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="10">
-        <v>68</v>
-      </c>
-      <c r="G10" s="10">
-        <v>68</v>
-      </c>
-      <c r="H10" s="11">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5">
-        <v>2</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="7">
-        <v>87.75</v>
-      </c>
-      <c r="G11" s="10">
-        <v>95375</v>
-      </c>
-      <c r="H11" s="11">
-        <v>183125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5">
-        <v>2</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="7">
-        <v>93.25</v>
-      </c>
-      <c r="G12" s="10">
+      <c r="C69" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E69" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="8">
-        <v>162.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5">
-        <v>2</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5">
-        <v>2</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="F69" s="16">
+        <v>8875</v>
+      </c>
+      <c r="G69" s="16">
+        <v>7625</v>
+      </c>
+      <c r="H69" s="14">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="11">
+        <v>69</v>
+      </c>
+      <c r="B70" s="11">
+        <v>9</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E70" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="7">
-        <v>92.25</v>
-      </c>
-      <c r="G14" s="10">
+      <c r="F70" s="16">
         <v>0</v>
       </c>
-      <c r="H14" s="8">
-        <v>92.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5">
-        <v>2</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="G70" s="16">
         <v>0</v>
       </c>
-      <c r="G15" s="10">
+      <c r="H70" s="17">
         <v>0</v>
       </c>
-      <c r="H15" s="11">
+    </row>
+    <row r="71" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="11">
+        <v>70</v>
+      </c>
+      <c r="B71" s="11">
+        <v>9</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F71" s="16">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5">
-        <v>2</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="10">
-        <v>59375</v>
-      </c>
-      <c r="G16" s="10">
-        <v>34375</v>
-      </c>
-      <c r="H16" s="8">
-        <v>93.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5">
-        <v>2</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="7">
-        <v>68.5</v>
-      </c>
-      <c r="G17" s="7">
+      <c r="G71" s="16">
         <v>0</v>
       </c>
-      <c r="H17" s="11">
-        <v>68.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5">
-        <v>3</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="7">
-        <v>70.5</v>
-      </c>
-      <c r="G18" s="7">
-        <v>70.5</v>
-      </c>
-      <c r="H18" s="11">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5">
-        <v>3</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="10">
-        <v>62</v>
-      </c>
-      <c r="G19" s="7">
-        <v>33.25</v>
-      </c>
-      <c r="H19" s="8">
-        <v>95.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5">
-        <v>3</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="10">
-        <v>68</v>
-      </c>
-      <c r="G20" s="7">
-        <v>30.25</v>
-      </c>
-      <c r="H20" s="8">
-        <v>98.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5">
-        <v>3</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="10">
-        <v>18</v>
-      </c>
-      <c r="G21" s="10">
-        <v>58</v>
-      </c>
-      <c r="H21" s="11">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5">
-        <v>3</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="10">
+      <c r="H71" s="17">
         <v>0</v>
       </c>
-      <c r="G22" s="10">
-        <v>66625</v>
-      </c>
-      <c r="H22" s="11">
-        <v>66625</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5">
-        <v>3</v>
-      </c>
-      <c r="C23" s="5" t="s">
+    </row>
+    <row r="72" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="11">
         <v>71</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="B72" s="11">
+        <v>9</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F72" s="16">
+        <v>0</v>
+      </c>
+      <c r="G72" s="16">
+        <v>0</v>
+      </c>
+      <c r="H72" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="11">
         <v>72</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="B73" s="11">
+        <v>9</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F73" s="16">
+        <v>0</v>
+      </c>
+      <c r="G73" s="16">
+        <v>0</v>
+      </c>
+      <c r="H73" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="11">
         <v>73</v>
       </c>
-      <c r="F23" s="10">
-        <v>68</v>
-      </c>
-      <c r="G23" s="10">
-        <v>72375</v>
-      </c>
-      <c r="H23" s="11">
-        <v>140375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5">
-        <v>3</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B74" s="11">
+        <v>9</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" s="18" t="str">
+        <f>CONCATENATE(Parejas!$C74," - ",Parejas!$D74)</f>
+        <v>Almudena - Inma Villacañas</v>
+      </c>
+      <c r="F74" s="16">
+        <v>0</v>
+      </c>
+      <c r="G74" s="16">
+        <v>0</v>
+      </c>
+      <c r="H74" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="11">
         <v>74</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="B75" s="11">
+        <v>9</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E75" s="18" t="str">
+        <f>CONCATENATE(Parejas!$C75," - ",Parejas!$D75)</f>
+        <v>Manuel Juarez - Antonio García</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0</v>
+      </c>
+      <c r="G75" s="6">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="11">
         <v>75</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="7">
-        <v>59.5</v>
-      </c>
-      <c r="G24" s="10">
+      <c r="B76" s="11">
+        <v>9</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E76" s="20" t="str">
+        <f>CONCATENATE(Parejas!$C76," - ",Parejas!$D76)</f>
+        <v>Mari Angeles - Laura</v>
+      </c>
+      <c r="F76" s="6">
         <v>0</v>
       </c>
-      <c r="H24" s="8">
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5">
-        <v>3</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="10">
-        <v>74</v>
-      </c>
-      <c r="G25" s="7">
-        <v>53.75</v>
-      </c>
-      <c r="H25" s="8">
-        <v>127.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5">
-        <v>4</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="10">
-        <v>55</v>
-      </c>
-      <c r="G26" s="7">
-        <v>59.5</v>
-      </c>
-      <c r="H26" s="8">
-        <v>114.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5">
-        <v>4</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="7">
-        <v>45.25</v>
-      </c>
-      <c r="G27" s="7">
-        <v>28.25</v>
-      </c>
-      <c r="H27" s="8">
-        <v>73.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>27</v>
-      </c>
-      <c r="B28" s="5">
-        <v>4</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="7">
-        <v>42.75</v>
-      </c>
-      <c r="G28" s="7">
-        <v>20.75</v>
-      </c>
-      <c r="H28" s="8">
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5">
-        <v>4</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="10">
-        <v>53125</v>
-      </c>
-      <c r="G29" s="10">
-        <v>23625</v>
-      </c>
-      <c r="H29" s="8">
-        <v>76.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
-        <v>29</v>
-      </c>
-      <c r="B30" s="5">
-        <v>4</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="7">
-        <v>43.5</v>
-      </c>
-      <c r="G30" s="7">
-        <v>43.5</v>
-      </c>
-      <c r="H30" s="11">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5">
-        <v>4</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="7">
-        <v>56.25</v>
-      </c>
-      <c r="G31" s="7">
-        <v>17.75</v>
-      </c>
-      <c r="H31" s="11">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5">
-        <v>4</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="10">
-        <v>45875</v>
-      </c>
-      <c r="G32" s="10">
-        <v>23875</v>
-      </c>
-      <c r="H32" s="8">
-        <v>69.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5">
-        <v>4</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="G76" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="7">
+      <c r="H76" s="6">
         <v>0</v>
       </c>
-      <c r="H33" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>33</v>
-      </c>
-      <c r="B34" s="5">
-        <v>5</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" s="10">
-        <v>41125</v>
-      </c>
-      <c r="G34" s="10">
-        <v>17625</v>
-      </c>
-      <c r="H34" s="8">
-        <v>58.75</v>
-      </c>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
-    </row>
-    <row r="35" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5">
-        <v>5</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F35" s="7">
-        <v>57.75</v>
-      </c>
-      <c r="G35" s="7">
-        <v>22.75</v>
-      </c>
-      <c r="H35" s="8">
-        <v>80.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
-        <v>35</v>
-      </c>
-      <c r="B36" s="5">
-        <v>5</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" s="7">
-        <v>39.75</v>
-      </c>
-      <c r="G36" s="7">
-        <v>39.75</v>
-      </c>
-      <c r="H36" s="8">
-        <v>79.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5">
-        <v>5</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37" s="7">
-        <v>35.25</v>
-      </c>
-      <c r="G37" s="7">
-        <v>15.5</v>
-      </c>
-      <c r="H37" s="8">
-        <v>50.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5">
-        <v>5</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="10">
-        <v>30125</v>
-      </c>
-      <c r="G38" s="10">
-        <v>30125</v>
-      </c>
-      <c r="H38" s="8">
-        <v>60.25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5">
-        <v>5</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="F39" s="10">
-        <v>42875</v>
-      </c>
-      <c r="G39" s="10">
-        <v>31875</v>
-      </c>
-      <c r="H39" s="8">
-        <v>74.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5">
-        <v>5</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F40" s="10">
-        <v>29875</v>
-      </c>
-      <c r="G40" s="10">
-        <v>29875</v>
-      </c>
-      <c r="H40" s="8">
-        <v>59.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5">
-        <v>5</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F41" s="10">
-        <v>34125</v>
-      </c>
-      <c r="G41" s="10">
-        <v>18125</v>
-      </c>
-      <c r="H41" s="8">
-        <v>52.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F42" s="10">
-        <v>28375</v>
-      </c>
-      <c r="G42" s="10">
-        <v>28375</v>
-      </c>
-      <c r="H42" s="8">
-        <v>56.75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F43" s="7">
-        <v>25.75</v>
-      </c>
-      <c r="G43" s="7">
-        <v>25.75</v>
-      </c>
-      <c r="H43" s="8">
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
-        <v>43</v>
-      </c>
-      <c r="B44" s="5">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="F44" s="7">
-        <v>28.25</v>
-      </c>
-      <c r="G44" s="7">
-        <v>28.25</v>
-      </c>
-      <c r="H44" s="8">
-        <v>56.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F45" s="7">
-        <v>18.5</v>
-      </c>
-      <c r="G45" s="7">
-        <v>18.5</v>
-      </c>
-      <c r="H45" s="11">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
-        <v>45</v>
-      </c>
-      <c r="B46" s="5">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="F46" s="10">
-        <v>26125</v>
-      </c>
-      <c r="G46" s="10">
-        <v>26125</v>
-      </c>
-      <c r="H46" s="8">
-        <v>52.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
-        <v>46</v>
-      </c>
-      <c r="B47" s="5">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F47" s="7">
-        <v>15.25</v>
-      </c>
-      <c r="G47" s="7">
-        <v>15.25</v>
-      </c>
-      <c r="H47" s="8">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5">
-        <v>47</v>
-      </c>
-      <c r="B48" s="5">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F48" s="10">
-        <v>24625</v>
-      </c>
-      <c r="G48" s="10">
-        <v>24625</v>
-      </c>
-      <c r="H48" s="8">
-        <v>49.25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5">
-        <v>48</v>
-      </c>
-      <c r="B49" s="5">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="F49" s="10">
-        <v>29</v>
-      </c>
-      <c r="G49" s="10">
-        <v>6125</v>
-      </c>
-      <c r="H49" s="11">
-        <v>35125</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="5">
-        <v>49</v>
-      </c>
-      <c r="B50" s="5">
-        <v>7</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="F50" s="10">
-        <v>0</v>
-      </c>
-      <c r="G50" s="10">
-        <v>20875</v>
-      </c>
-      <c r="H50" s="11">
-        <v>20875</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="5">
-        <v>50</v>
-      </c>
-      <c r="B51" s="5">
-        <v>7</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E51" s="12" t="str">
-        <f>CONCATENATE(Parejas!$C51," - ",Parejas!$D51)</f>
-        <v>Nicanor Hermosilla - J. Antonio Berdonces</v>
-      </c>
-      <c r="F51" s="10">
-        <v>0</v>
-      </c>
-      <c r="G51" s="10">
-        <v>0</v>
-      </c>
-      <c r="H51" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5">
-        <v>51</v>
-      </c>
-      <c r="B52" s="5">
-        <v>7</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E52" s="15" t="str">
-        <f>CONCATENATE(Parejas!$C52," - ",Parejas!$D52)</f>
-        <v>David Camara - Adrian Sáez</v>
-      </c>
-      <c r="F52" s="13">
-        <v>0</v>
-      </c>
-      <c r="G52" s="13">
-        <v>0</v>
-      </c>
-      <c r="H52" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="5">
-        <v>52</v>
-      </c>
-      <c r="B53" s="5">
-        <v>7</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F53" s="7">
-        <v>17.25</v>
-      </c>
-      <c r="G53" s="7">
-        <v>5.75</v>
-      </c>
-      <c r="H53" s="11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5">
-        <v>53</v>
-      </c>
-      <c r="B54" s="5">
-        <v>7</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F54" s="7">
-        <v>22.5</v>
-      </c>
-      <c r="G54" s="10">
-        <v>9</v>
-      </c>
-      <c r="H54" s="8">
-        <v>31.5</v>
-      </c>
-      <c r="K54" s="13"/>
-    </row>
-    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
-        <v>54</v>
-      </c>
-      <c r="B55" s="5">
-        <v>7</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F55" s="7">
-        <v>12.5</v>
-      </c>
-      <c r="G55" s="7">
-        <v>12.5</v>
-      </c>
-      <c r="H55" s="11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5">
-        <v>55</v>
-      </c>
-      <c r="B56" s="5">
-        <v>7</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F56" s="7">
-        <v>12.75</v>
-      </c>
-      <c r="G56" s="7">
-        <v>5.25</v>
-      </c>
-      <c r="H56" s="11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
-        <v>56</v>
-      </c>
-      <c r="B57" s="5">
-        <v>7</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F57" s="7">
-        <v>15.75</v>
-      </c>
-      <c r="G57" s="7">
-        <v>15.75</v>
-      </c>
-      <c r="H57" s="8">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="5">
-        <v>57</v>
-      </c>
-      <c r="B58" s="5">
-        <v>8</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="F58" s="10">
-        <v>12125</v>
-      </c>
-      <c r="G58" s="10">
-        <v>12125</v>
-      </c>
-      <c r="H58" s="8">
-        <v>24.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
-        <v>58</v>
-      </c>
-      <c r="B59" s="5">
-        <v>8</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F59" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="G59" s="10">
-        <v>18125</v>
-      </c>
-      <c r="H59" s="11">
-        <v>25625</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
-        <v>59</v>
-      </c>
-      <c r="B60" s="5">
-        <v>8</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F60" s="10">
-        <v>17125</v>
-      </c>
-      <c r="G60" s="10">
-        <v>17125</v>
-      </c>
-      <c r="H60" s="8">
-        <v>34.25</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
-        <v>60</v>
-      </c>
-      <c r="B61" s="5">
-        <v>8</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="F61" s="7">
-        <v>8.75</v>
-      </c>
-      <c r="G61" s="7">
-        <v>8.75</v>
-      </c>
-      <c r="H61" s="8">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
-        <v>61</v>
-      </c>
-      <c r="B62" s="5">
-        <v>8</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="E62" s="12" t="str">
-        <f>CONCATENATE(Parejas!$C62," - ",Parejas!$D62)</f>
-        <v>Miguel Marmol - Fernando Cubero</v>
-      </c>
-      <c r="F62" s="10">
-        <v>0</v>
-      </c>
-      <c r="G62" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="H62" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
-        <v>62</v>
-      </c>
-      <c r="B63" s="5">
-        <v>8</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F63" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="G63" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="H63" s="11">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
-        <v>63</v>
-      </c>
-      <c r="B64" s="5">
-        <v>8</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E64" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="F64" s="10">
-        <v>11</v>
-      </c>
-      <c r="G64" s="10">
-        <v>11</v>
-      </c>
-      <c r="H64" s="11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
-        <v>64</v>
-      </c>
-      <c r="B65" s="5">
-        <v>8</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="F65" s="10">
-        <v>8875</v>
-      </c>
-      <c r="G65" s="10">
-        <v>7625</v>
-      </c>
-      <c r="H65" s="8">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
-        <v>65</v>
-      </c>
-      <c r="B66" s="5">
-        <v>9</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F66" s="10">
-        <v>11125</v>
-      </c>
-      <c r="G66" s="10">
-        <v>14875</v>
-      </c>
-      <c r="H66" s="11">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
-        <v>66</v>
-      </c>
-      <c r="B67" s="5">
-        <v>9</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="F67" s="10">
-        <v>0</v>
-      </c>
-      <c r="G67" s="10">
-        <v>0</v>
-      </c>
-      <c r="H67" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
-        <v>67</v>
-      </c>
-      <c r="B68" s="5">
-        <v>9</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="F68" s="10">
-        <v>0</v>
-      </c>
-      <c r="G68" s="10">
-        <v>0</v>
-      </c>
-      <c r="H68" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
-        <v>68</v>
-      </c>
-      <c r="B69" s="5">
-        <v>9</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="F69" s="10">
-        <v>0</v>
-      </c>
-      <c r="G69" s="10">
-        <v>0</v>
-      </c>
-      <c r="H69" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
-        <v>69</v>
-      </c>
-      <c r="B70" s="5">
-        <v>9</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F70" s="10">
-        <v>0</v>
-      </c>
-      <c r="G70" s="10">
-        <v>0</v>
-      </c>
-      <c r="H70" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="5">
-        <v>70</v>
-      </c>
-      <c r="B71" s="5">
-        <v>9</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E71" s="12" t="str">
-        <f>CONCATENATE(Parejas!$C71," - ",Parejas!$D71)</f>
-        <v>Almudena - Inma Villacañas</v>
-      </c>
-      <c r="F71" s="10">
-        <v>0</v>
-      </c>
-      <c r="G71" s="10">
-        <v>0</v>
-      </c>
-      <c r="H71" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
     <row r="77" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="78" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4258,11 +5406,14 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{7CA3FEC5-A438-4C76-BE95-94AF2C9DD9DC}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{455FAC2B-6350-4C42-98AE-AB0163447A05}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:E71" xr:uid="{4CEFA24F-2DE2-475D-982C-17AAF0214D2E}"/>
+      <autoFilter ref="A1:E76" xr:uid="{003909F2-9F1B-493A-94BB-7E1747BD0887}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="689686766"/>
@@ -4281,8 +5432,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4293,370 +5444,370 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="A1" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="23"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="23"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="25">
+        <v>27</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" s="18"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="B11" s="25">
+        <v>55</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="25">
+        <v>69</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="26">
+        <v>3875</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="26">
+        <v>3875</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="25">
+        <v>58</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B16" s="25">
+        <v>68</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B20" s="26">
+        <v>80625</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B21" s="25">
+        <v>17</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" s="25">
+        <v>17</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="26">
+        <v>19375</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B24" s="26">
+        <v>39875</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" s="6">
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" s="6">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B27" s="6">
+        <v>68.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B28" s="6">
+        <v>6.125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B29" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B30" s="6">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="B31" s="28">
+        <v>40.875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="18"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="20">
-        <v>27</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="B32" s="6">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B33" s="6">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="B34" s="6">
+        <v>82.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="B35" s="6">
         <v>53</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" s="20">
-        <v>55</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="20">
-        <v>69</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" s="21">
-        <v>3875</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B14" s="21">
-        <v>3875</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="20">
-        <v>58</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" s="20">
-        <v>68</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B20" s="21">
-        <v>80625</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B21" s="20">
-        <v>17</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B22" s="20">
-        <v>17</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="21">
-        <v>19375</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24" s="21">
-        <v>39875</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="B25" s="13">
-        <v>38.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="B26" s="13">
-        <v>58.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="B27" s="13">
-        <v>68.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="B28" s="13">
-        <v>6.125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="B29" s="13">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B30" s="13">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="B31" s="23">
-        <v>40.875</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="B32" s="13">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="B33" s="13">
-        <v>40.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="B34" s="13">
-        <v>82.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="B35" s="13">
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B36" s="6">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="B36" s="13">
-        <v>53</v>
-      </c>
-    </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="B37" s="13">
+      <c r="A37" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="B37" s="6">
         <v>67.5</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="B38" s="13">
+      <c r="A38" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B38" s="6">
         <v>67.5</v>
       </c>
     </row>
